--- a/source/bin/excel/animation.xlsx
+++ b/source/bin/excel/animation.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29029"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\liqi-excel\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5C99A48-4DF4-49EA-8D81-1CC4724E2982}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22998945-3C76-4E64-AE41-136D0C95FF2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,8 +26,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -35,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="66">
   <si>
     <t>sheet</t>
   </si>
@@ -241,6 +239,22 @@
   </si>
   <si>
     <t>hand_archer</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>hand_bantianyinshi</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>hand_guixiaotailang</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>hand_gaoshanjinzhu</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>hand_banbenchenma</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -279,24 +293,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFF66FF"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -311,15 +313,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -636,698 +635,699 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:O98"/>
+  <dimension ref="A1:O118"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="13.375" customWidth="1"/>
-    <col min="2" max="3" width="12" customWidth="1"/>
-    <col min="4" max="4" width="20" customWidth="1"/>
-    <col min="5" max="5" width="26.625" customWidth="1"/>
-    <col min="6" max="6" width="21" customWidth="1"/>
-    <col min="7" max="15" width="12.75" customWidth="1"/>
-    <col min="16" max="16" width="10.375" customWidth="1"/>
-    <col min="17" max="17" width="9.125" customWidth="1"/>
-    <col min="18" max="18" width="9" customWidth="1"/>
-    <col min="19" max="19" width="10.375" customWidth="1"/>
-    <col min="20" max="20" width="13" customWidth="1"/>
-    <col min="21" max="21" width="5.5" customWidth="1"/>
-    <col min="22" max="22" width="12.625" customWidth="1"/>
-    <col min="23" max="23" width="13" customWidth="1"/>
+    <col min="1" max="1" width="13.375" style="3" customWidth="1"/>
+    <col min="2" max="3" width="12" style="3" customWidth="1"/>
+    <col min="4" max="4" width="20" style="3" customWidth="1"/>
+    <col min="5" max="5" width="26.625" style="3" customWidth="1"/>
+    <col min="6" max="6" width="21" style="3" customWidth="1"/>
+    <col min="7" max="15" width="12.75" style="3" customWidth="1"/>
+    <col min="16" max="16" width="10.375" style="3" customWidth="1"/>
+    <col min="17" max="17" width="9.125" style="3" customWidth="1"/>
+    <col min="18" max="18" width="9" style="3" customWidth="1"/>
+    <col min="19" max="19" width="10.375" style="3" customWidth="1"/>
+    <col min="20" max="20" width="13" style="3" customWidth="1"/>
+    <col min="21" max="21" width="5.5" style="3" customWidth="1"/>
+    <col min="22" max="22" width="12.625" style="3" customWidth="1"/>
+    <col min="23" max="23" width="13" style="3" customWidth="1"/>
+    <col min="24" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="O1" s="2" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="E2" t="s">
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="E2" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="F2" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="G2" s="2" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="F3" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="G3" s="2" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A4" s="1"/>
-      <c r="B4" s="1">
+      <c r="A4" s="2"/>
+      <c r="B4" s="2">
         <v>1000101</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="E4">
+      <c r="E4" s="3">
         <v>460</v>
       </c>
-      <c r="F4">
+      <c r="F4" s="3">
         <v>0.94</v>
       </c>
-      <c r="G4">
+      <c r="G4" s="3">
         <v>319</v>
       </c>
-      <c r="H4">
+      <c r="H4" s="3">
         <v>319</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A5" s="1"/>
-      <c r="B5" s="1">
+      <c r="A5" s="2"/>
+      <c r="B5" s="2">
         <v>1000102</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="E5">
+      <c r="E5" s="3">
         <v>1615</v>
       </c>
-      <c r="F5">
+      <c r="F5" s="3">
         <v>2</v>
       </c>
-      <c r="G5">
+      <c r="G5" s="3">
         <v>550</v>
       </c>
-      <c r="H5">
+      <c r="H5" s="3">
         <v>1300</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A6" s="1"/>
-      <c r="B6" s="1">
+      <c r="A6" s="2"/>
+      <c r="B6" s="2">
         <v>1000103</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C6" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D6" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="E6">
-        <v>800</v>
-      </c>
-      <c r="F6">
-        <v>1</v>
-      </c>
-      <c r="G6">
+      <c r="E6" s="3">
+        <v>800</v>
+      </c>
+      <c r="F6" s="3">
+        <v>1</v>
+      </c>
+      <c r="G6" s="3">
         <v>500</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A7" s="1"/>
-      <c r="B7" s="1">
+      <c r="A7" s="2"/>
+      <c r="B7" s="2">
         <v>1000104</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="C7" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D7" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="E7">
-        <v>900</v>
-      </c>
-      <c r="F7">
+      <c r="E7" s="3">
+        <v>900</v>
+      </c>
+      <c r="F7" s="3">
         <v>2</v>
       </c>
-      <c r="G7">
+      <c r="G7" s="3">
         <v>150</v>
       </c>
-      <c r="H7">
+      <c r="H7" s="3">
         <v>733</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A8" s="1"/>
-      <c r="B8" s="1">
+      <c r="A8" s="2"/>
+      <c r="B8" s="2">
         <v>1000105</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="C8" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="D8" t="s">
+      <c r="D8" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="E8">
-        <v>900</v>
-      </c>
-      <c r="F8">
-        <v>1</v>
-      </c>
-      <c r="G8">
+      <c r="E8" s="3">
+        <v>900</v>
+      </c>
+      <c r="F8" s="3">
+        <v>1</v>
+      </c>
+      <c r="G8" s="3">
         <v>450</v>
       </c>
-      <c r="H8">
+      <c r="H8" s="3">
         <v>900</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A9" s="1"/>
-      <c r="B9" s="1">
+      <c r="A9" s="2"/>
+      <c r="B9" s="2">
         <v>1000201</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="C9" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="D9" t="s">
+      <c r="D9" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="E9">
-        <v>500</v>
-      </c>
-      <c r="F9">
+      <c r="E9" s="3">
+        <v>500</v>
+      </c>
+      <c r="F9" s="3">
         <v>0.85</v>
       </c>
-      <c r="G9">
+      <c r="G9" s="3">
         <v>319</v>
       </c>
-      <c r="H9">
+      <c r="H9" s="3">
         <v>319</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A10" s="1"/>
-      <c r="B10" s="1">
+      <c r="A10" s="2"/>
+      <c r="B10" s="2">
         <v>1000202</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="C10" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="D10" t="s">
+      <c r="D10" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="E10">
-        <v>900</v>
-      </c>
-      <c r="F10">
+      <c r="E10" s="3">
+        <v>900</v>
+      </c>
+      <c r="F10" s="3">
         <v>1.2</v>
       </c>
-      <c r="G10">
+      <c r="G10" s="3">
         <v>400</v>
       </c>
-      <c r="H10">
+      <c r="H10" s="3">
         <v>720</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A11" s="1"/>
-      <c r="B11" s="1">
+      <c r="A11" s="2"/>
+      <c r="B11" s="2">
         <v>1000203</v>
       </c>
-      <c r="C11" s="1" t="s">
+      <c r="C11" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="D11" s="5" t="s">
+      <c r="D11" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="E11">
-        <v>800</v>
-      </c>
-      <c r="F11">
-        <v>1</v>
-      </c>
-      <c r="G11">
+      <c r="E11" s="3">
+        <v>800</v>
+      </c>
+      <c r="F11" s="3">
+        <v>1</v>
+      </c>
+      <c r="G11" s="3">
         <v>500</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A12" s="1"/>
-      <c r="B12" s="1">
+      <c r="A12" s="2"/>
+      <c r="B12" s="2">
         <v>1000204</v>
       </c>
-      <c r="C12" s="1" t="s">
+      <c r="C12" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="D12" t="s">
+      <c r="D12" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="E12">
-        <v>900</v>
-      </c>
-      <c r="F12">
+      <c r="E12" s="3">
+        <v>900</v>
+      </c>
+      <c r="F12" s="3">
         <v>2</v>
       </c>
-      <c r="G12">
+      <c r="G12" s="3">
         <v>150</v>
       </c>
-      <c r="H12">
+      <c r="H12" s="3">
         <v>733</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A13" s="1"/>
-      <c r="B13" s="1">
+      <c r="A13" s="2"/>
+      <c r="B13" s="2">
         <v>1000205</v>
       </c>
-      <c r="C13" s="1" t="s">
+      <c r="C13" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="D13" t="s">
+      <c r="D13" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="E13">
-        <v>900</v>
-      </c>
-      <c r="F13">
-        <v>1</v>
-      </c>
-      <c r="G13">
+      <c r="E13" s="3">
+        <v>900</v>
+      </c>
+      <c r="F13" s="3">
+        <v>1</v>
+      </c>
+      <c r="G13" s="3">
         <v>450</v>
       </c>
-      <c r="H13">
+      <c r="H13" s="3">
         <v>900</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A14" s="1"/>
-      <c r="B14" s="1">
+      <c r="A14" s="2"/>
+      <c r="B14" s="2">
         <v>1000301</v>
       </c>
-      <c r="C14" s="1" t="s">
+      <c r="C14" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="D14" t="s">
+      <c r="D14" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="E14">
-        <v>500</v>
-      </c>
-      <c r="F14">
+      <c r="E14" s="3">
+        <v>500</v>
+      </c>
+      <c r="F14" s="3">
         <v>0.85</v>
       </c>
-      <c r="G14">
+      <c r="G14" s="3">
         <v>319</v>
       </c>
-      <c r="H14">
+      <c r="H14" s="3">
         <v>319</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A15" s="1"/>
-      <c r="B15" s="1">
+      <c r="A15" s="2"/>
+      <c r="B15" s="2">
         <v>1000302</v>
       </c>
-      <c r="C15" s="1" t="s">
+      <c r="C15" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="D15" t="s">
+      <c r="D15" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="E15">
-        <v>900</v>
-      </c>
-      <c r="F15">
+      <c r="E15" s="3">
+        <v>900</v>
+      </c>
+      <c r="F15" s="3">
         <v>1.2</v>
       </c>
-      <c r="G15">
+      <c r="G15" s="3">
         <v>400</v>
       </c>
-      <c r="H15">
+      <c r="H15" s="3">
         <v>720</v>
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A16" s="1"/>
-      <c r="B16" s="1">
+      <c r="A16" s="2"/>
+      <c r="B16" s="2">
         <v>1000303</v>
       </c>
-      <c r="C16" s="1" t="s">
+      <c r="C16" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="D16" t="s">
+      <c r="D16" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="E16">
-        <v>800</v>
-      </c>
-      <c r="F16">
-        <v>1</v>
-      </c>
-      <c r="G16">
+      <c r="E16" s="3">
+        <v>800</v>
+      </c>
+      <c r="F16" s="3">
+        <v>1</v>
+      </c>
+      <c r="G16" s="3">
         <v>500</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A17" s="1"/>
-      <c r="B17" s="1">
+      <c r="A17" s="2"/>
+      <c r="B17" s="2">
         <v>1000304</v>
       </c>
-      <c r="C17" s="1" t="s">
+      <c r="C17" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="D17" t="s">
+      <c r="D17" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="E17">
-        <v>900</v>
-      </c>
-      <c r="F17">
+      <c r="E17" s="3">
+        <v>900</v>
+      </c>
+      <c r="F17" s="3">
         <v>2</v>
       </c>
-      <c r="G17">
+      <c r="G17" s="3">
         <v>150</v>
       </c>
-      <c r="H17">
+      <c r="H17" s="3">
         <v>733</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A18" s="1"/>
-      <c r="B18" s="1">
+      <c r="A18" s="2"/>
+      <c r="B18" s="2">
         <v>1000305</v>
       </c>
-      <c r="C18" s="1" t="s">
+      <c r="C18" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="D18" t="s">
+      <c r="D18" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="E18">
-        <v>900</v>
-      </c>
-      <c r="F18">
-        <v>1</v>
-      </c>
-      <c r="G18">
+      <c r="E18" s="3">
+        <v>900</v>
+      </c>
+      <c r="F18" s="3">
+        <v>1</v>
+      </c>
+      <c r="G18" s="3">
         <v>450</v>
       </c>
-      <c r="H18">
+      <c r="H18" s="3">
         <v>900</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A19" s="1"/>
-      <c r="B19" s="1">
+      <c r="A19" s="2"/>
+      <c r="B19" s="2">
         <v>1000401</v>
       </c>
-      <c r="C19" s="1" t="s">
+      <c r="C19" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="D19" t="s">
+      <c r="D19" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="E19">
-        <v>500</v>
-      </c>
-      <c r="F19">
+      <c r="E19" s="3">
+        <v>500</v>
+      </c>
+      <c r="F19" s="3">
         <v>0.85</v>
       </c>
-      <c r="G19">
+      <c r="G19" s="3">
         <v>319</v>
       </c>
-      <c r="H19">
+      <c r="H19" s="3">
         <v>319</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A20" s="1"/>
-      <c r="B20" s="1">
+      <c r="A20" s="2"/>
+      <c r="B20" s="2">
         <v>1000402</v>
       </c>
-      <c r="C20" s="1" t="s">
+      <c r="C20" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="D20" t="s">
+      <c r="D20" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="E20">
-        <v>900</v>
-      </c>
-      <c r="F20">
+      <c r="E20" s="3">
+        <v>900</v>
+      </c>
+      <c r="F20" s="3">
         <v>1.2</v>
       </c>
-      <c r="G20">
+      <c r="G20" s="3">
         <v>400</v>
       </c>
-      <c r="H20">
+      <c r="H20" s="3">
         <v>720</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A21" s="1"/>
-      <c r="B21" s="1">
+      <c r="A21" s="2"/>
+      <c r="B21" s="2">
         <v>1000403</v>
       </c>
-      <c r="C21" s="1" t="s">
+      <c r="C21" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="D21" t="s">
+      <c r="D21" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="E21">
-        <v>800</v>
-      </c>
-      <c r="F21">
-        <v>1</v>
-      </c>
-      <c r="G21">
+      <c r="E21" s="3">
+        <v>800</v>
+      </c>
+      <c r="F21" s="3">
+        <v>1</v>
+      </c>
+      <c r="G21" s="3">
         <v>500</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A22" s="1"/>
-      <c r="B22" s="1">
+      <c r="A22" s="2"/>
+      <c r="B22" s="2">
         <v>1000404</v>
       </c>
-      <c r="C22" s="1" t="s">
+      <c r="C22" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="D22" t="s">
+      <c r="D22" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="E22">
-        <v>900</v>
-      </c>
-      <c r="F22">
+      <c r="E22" s="3">
+        <v>900</v>
+      </c>
+      <c r="F22" s="3">
         <v>2</v>
       </c>
-      <c r="G22">
+      <c r="G22" s="3">
         <v>150</v>
       </c>
-      <c r="H22">
+      <c r="H22" s="3">
         <v>733</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A23" s="1"/>
-      <c r="B23" s="1">
+      <c r="A23" s="2"/>
+      <c r="B23" s="2">
         <v>1000405</v>
       </c>
-      <c r="C23" s="1" t="s">
+      <c r="C23" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="D23" t="s">
+      <c r="D23" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="E23">
-        <v>900</v>
-      </c>
-      <c r="F23">
-        <v>1</v>
-      </c>
-      <c r="G23">
+      <c r="E23" s="3">
+        <v>900</v>
+      </c>
+      <c r="F23" s="3">
+        <v>1</v>
+      </c>
+      <c r="G23" s="3">
         <v>450</v>
       </c>
-      <c r="H23">
+      <c r="H23" s="3">
         <v>900</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A24" s="1"/>
-      <c r="B24" s="1">
+      <c r="A24" s="2"/>
+      <c r="B24" s="2">
         <v>1000501</v>
       </c>
-      <c r="C24" s="1" t="s">
+      <c r="C24" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="D24" t="s">
+      <c r="D24" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="E24">
+      <c r="E24" s="3">
         <v>533</v>
       </c>
-      <c r="F24">
-        <v>1</v>
-      </c>
-      <c r="G24">
+      <c r="F24" s="3">
+        <v>1</v>
+      </c>
+      <c r="G24" s="3">
         <v>260</v>
       </c>
-      <c r="H24">
+      <c r="H24" s="3">
         <v>260</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A25" s="1"/>
-      <c r="B25" s="1">
+      <c r="A25" s="2"/>
+      <c r="B25" s="2">
         <v>1000502</v>
       </c>
-      <c r="C25" s="1" t="s">
+      <c r="C25" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="D25" t="s">
+      <c r="D25" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="E25">
-        <v>900</v>
-      </c>
-      <c r="F25">
-        <v>1</v>
-      </c>
-      <c r="G25">
+      <c r="E25" s="3">
+        <v>900</v>
+      </c>
+      <c r="F25" s="3">
+        <v>1</v>
+      </c>
+      <c r="G25" s="3">
         <v>270</v>
       </c>
-      <c r="H25">
+      <c r="H25" s="3">
         <v>650</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A26" s="1"/>
-      <c r="B26" s="1">
+      <c r="A26" s="2"/>
+      <c r="B26" s="2">
         <v>1000503</v>
       </c>
-      <c r="C26" s="1" t="s">
+      <c r="C26" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="D26" t="s">
+      <c r="D26" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="E26">
-        <v>800</v>
-      </c>
-      <c r="F26">
-        <v>1</v>
-      </c>
-      <c r="G26">
+      <c r="E26" s="3">
+        <v>800</v>
+      </c>
+      <c r="F26" s="3">
+        <v>1</v>
+      </c>
+      <c r="G26" s="3">
         <v>500</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A27" s="1"/>
-      <c r="B27" s="1">
+      <c r="A27" s="2"/>
+      <c r="B27" s="2">
         <v>1000504</v>
       </c>
-      <c r="C27" s="1" t="s">
+      <c r="C27" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="D27" t="s">
+      <c r="D27" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="E27">
-        <v>900</v>
-      </c>
-      <c r="F27">
+      <c r="E27" s="3">
+        <v>900</v>
+      </c>
+      <c r="F27" s="3">
         <v>2</v>
       </c>
-      <c r="G27">
+      <c r="G27" s="3">
         <v>150</v>
       </c>
-      <c r="H27">
+      <c r="H27" s="3">
         <v>733</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A28" s="1"/>
-      <c r="B28" s="1">
+      <c r="A28" s="2"/>
+      <c r="B28" s="2">
         <v>1000505</v>
       </c>
-      <c r="C28" s="1" t="s">
+      <c r="C28" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="D28" t="s">
+      <c r="D28" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="E28">
-        <v>900</v>
-      </c>
-      <c r="F28">
-        <v>1</v>
-      </c>
-      <c r="G28">
+      <c r="E28" s="3">
+        <v>900</v>
+      </c>
+      <c r="F28" s="3">
+        <v>1</v>
+      </c>
+      <c r="G28" s="3">
         <v>450</v>
       </c>
-      <c r="H28">
+      <c r="H28" s="3">
         <v>900</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A29" s="1"/>
+      <c r="A29" s="2"/>
       <c r="B29" s="2">
         <v>1000601</v>
       </c>
@@ -1351,7 +1351,7 @@
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A30" s="1"/>
+      <c r="A30" s="2"/>
       <c r="B30" s="2">
         <v>1000602</v>
       </c>
@@ -1375,7 +1375,7 @@
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A31" s="1"/>
+      <c r="A31" s="2"/>
       <c r="B31" s="2">
         <v>1000603</v>
       </c>
@@ -1394,10 +1394,9 @@
       <c r="G31" s="3">
         <v>500</v>
       </c>
-      <c r="H31" s="3"/>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A32" s="1"/>
+      <c r="A32" s="2"/>
       <c r="B32" s="2">
         <v>1000604</v>
       </c>
@@ -1421,7 +1420,7 @@
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A33" s="1"/>
+      <c r="A33" s="2"/>
       <c r="B33" s="2">
         <v>1000605</v>
       </c>
@@ -1445,7 +1444,7 @@
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A34" s="1"/>
+      <c r="A34" s="2"/>
       <c r="B34" s="2">
         <v>1000701</v>
       </c>
@@ -1469,7 +1468,7 @@
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A35" s="1"/>
+      <c r="A35" s="2"/>
       <c r="B35" s="2">
         <v>1000702</v>
       </c>
@@ -1493,7 +1492,7 @@
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A36" s="1"/>
+      <c r="A36" s="2"/>
       <c r="B36" s="2">
         <v>1000703</v>
       </c>
@@ -1512,10 +1511,9 @@
       <c r="G36" s="3">
         <v>500</v>
       </c>
-      <c r="H36" s="3"/>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A37" s="1"/>
+      <c r="A37" s="2"/>
       <c r="B37" s="2">
         <v>1000704</v>
       </c>
@@ -1539,7 +1537,7 @@
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A38" s="1"/>
+      <c r="A38" s="2"/>
       <c r="B38" s="2">
         <v>1000705</v>
       </c>
@@ -1563,131 +1561,131 @@
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A39" s="1"/>
-      <c r="B39" s="1">
+      <c r="A39" s="2"/>
+      <c r="B39" s="2">
         <v>1000801</v>
       </c>
-      <c r="C39" s="1" t="s">
+      <c r="C39" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="D39" t="s">
+      <c r="D39" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="E39">
+      <c r="E39" s="3">
         <v>460</v>
       </c>
-      <c r="F39">
+      <c r="F39" s="3">
         <v>0.94</v>
       </c>
-      <c r="G39">
+      <c r="G39" s="3">
         <v>319</v>
       </c>
-      <c r="H39">
+      <c r="H39" s="3">
         <v>319</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A40" s="1"/>
-      <c r="B40" s="1">
+      <c r="A40" s="2"/>
+      <c r="B40" s="2">
         <v>1000802</v>
       </c>
-      <c r="C40" s="1" t="s">
+      <c r="C40" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="D40" t="s">
+      <c r="D40" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="E40">
+      <c r="E40" s="3">
         <v>1615</v>
       </c>
-      <c r="F40">
+      <c r="F40" s="3">
         <v>2</v>
       </c>
-      <c r="G40">
+      <c r="G40" s="3">
         <v>550</v>
       </c>
-      <c r="H40">
+      <c r="H40" s="3">
         <v>1300</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A41" s="1"/>
-      <c r="B41" s="1">
+      <c r="A41" s="2"/>
+      <c r="B41" s="2">
         <v>1000803</v>
       </c>
-      <c r="C41" s="1" t="s">
+      <c r="C41" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="D41" t="s">
+      <c r="D41" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="E41">
-        <v>800</v>
-      </c>
-      <c r="F41">
-        <v>1</v>
-      </c>
-      <c r="G41">
+      <c r="E41" s="3">
+        <v>800</v>
+      </c>
+      <c r="F41" s="3">
+        <v>1</v>
+      </c>
+      <c r="G41" s="3">
         <v>500</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A42" s="1"/>
-      <c r="B42" s="1">
+      <c r="A42" s="2"/>
+      <c r="B42" s="2">
         <v>1000804</v>
       </c>
-      <c r="C42" s="1" t="s">
+      <c r="C42" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="D42" t="s">
+      <c r="D42" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="E42">
-        <v>900</v>
-      </c>
-      <c r="F42">
+      <c r="E42" s="3">
+        <v>900</v>
+      </c>
+      <c r="F42" s="3">
         <v>2</v>
       </c>
-      <c r="G42">
+      <c r="G42" s="3">
         <v>150</v>
       </c>
-      <c r="H42">
+      <c r="H42" s="3">
         <v>733</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A43" s="1"/>
-      <c r="B43" s="1">
+      <c r="A43" s="2"/>
+      <c r="B43" s="2">
         <v>1000805</v>
       </c>
-      <c r="C43" s="1" t="s">
+      <c r="C43" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="D43" t="s">
+      <c r="D43" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="E43">
-        <v>900</v>
-      </c>
-      <c r="F43">
-        <v>1</v>
-      </c>
-      <c r="G43">
+      <c r="E43" s="3">
+        <v>900</v>
+      </c>
+      <c r="F43" s="3">
+        <v>1</v>
+      </c>
+      <c r="G43" s="3">
         <v>450</v>
       </c>
-      <c r="H43">
+      <c r="H43" s="3">
         <v>900</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A44" s="1"/>
-      <c r="B44" s="1">
+      <c r="A44" s="2"/>
+      <c r="B44" s="2">
         <v>1000901</v>
       </c>
-      <c r="C44" s="1" t="s">
+      <c r="C44" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="D44" t="s">
+      <c r="D44" s="3" t="s">
         <v>41</v>
       </c>
       <c r="E44" s="3">
@@ -1704,14 +1702,14 @@
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A45" s="1"/>
-      <c r="B45" s="1">
+      <c r="A45" s="2"/>
+      <c r="B45" s="2">
         <v>1000902</v>
       </c>
-      <c r="C45" s="1" t="s">
+      <c r="C45" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="D45" t="s">
+      <c r="D45" s="3" t="s">
         <v>41</v>
       </c>
       <c r="E45" s="3">
@@ -1728,14 +1726,14 @@
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A46" s="1"/>
-      <c r="B46" s="1">
+      <c r="A46" s="2"/>
+      <c r="B46" s="2">
         <v>1000903</v>
       </c>
-      <c r="C46" s="1" t="s">
+      <c r="C46" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="D46" t="s">
+      <c r="D46" s="3" t="s">
         <v>41</v>
       </c>
       <c r="E46" s="3">
@@ -1747,17 +1745,16 @@
       <c r="G46" s="3">
         <v>500</v>
       </c>
-      <c r="H46" s="3"/>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A47" s="1"/>
-      <c r="B47" s="1">
+      <c r="A47" s="2"/>
+      <c r="B47" s="2">
         <v>1000904</v>
       </c>
-      <c r="C47" s="1" t="s">
+      <c r="C47" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="D47" t="s">
+      <c r="D47" s="3" t="s">
         <v>41</v>
       </c>
       <c r="E47" s="3">
@@ -1774,14 +1771,14 @@
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A48" s="1"/>
-      <c r="B48" s="1">
+      <c r="A48" s="2"/>
+      <c r="B48" s="2">
         <v>1000905</v>
       </c>
-      <c r="C48" s="1" t="s">
+      <c r="C48" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="D48" t="s">
+      <c r="D48" s="3" t="s">
         <v>41</v>
       </c>
       <c r="E48" s="3">
@@ -1798,7 +1795,7 @@
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A49" s="1"/>
+      <c r="A49" s="2"/>
       <c r="B49" s="2">
         <v>1001001</v>
       </c>
@@ -1822,7 +1819,7 @@
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A50" s="1"/>
+      <c r="A50" s="2"/>
       <c r="B50" s="2">
         <v>1001002</v>
       </c>
@@ -1846,7 +1843,7 @@
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A51" s="1"/>
+      <c r="A51" s="2"/>
       <c r="B51" s="2">
         <v>1001003</v>
       </c>
@@ -1865,7 +1862,6 @@
       <c r="G51" s="3">
         <v>500</v>
       </c>
-      <c r="H51" s="3"/>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B52" s="2">
@@ -1914,237 +1910,237 @@
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B54" s="1">
+      <c r="B54" s="2">
         <v>1001101</v>
       </c>
-      <c r="C54" s="1" t="s">
+      <c r="C54" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="D54" t="s">
+      <c r="D54" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="E54">
-        <v>500</v>
-      </c>
-      <c r="F54">
+      <c r="E54" s="3">
+        <v>500</v>
+      </c>
+      <c r="F54" s="3">
         <v>0.85</v>
       </c>
-      <c r="G54">
+      <c r="G54" s="3">
         <v>319</v>
       </c>
-      <c r="H54">
+      <c r="H54" s="3">
         <v>319</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B55" s="1">
+      <c r="B55" s="2">
         <v>1001102</v>
       </c>
-      <c r="C55" s="1" t="s">
+      <c r="C55" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="D55" s="5" t="s">
+      <c r="D55" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="E55">
-        <v>900</v>
-      </c>
-      <c r="F55">
+      <c r="E55" s="3">
+        <v>900</v>
+      </c>
+      <c r="F55" s="3">
         <v>1.2</v>
       </c>
-      <c r="G55">
+      <c r="G55" s="3">
         <v>400</v>
       </c>
-      <c r="H55">
+      <c r="H55" s="3">
         <v>720</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B56" s="1">
+      <c r="B56" s="2">
         <v>1001103</v>
       </c>
-      <c r="C56" s="1" t="s">
+      <c r="C56" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="D56" t="s">
+      <c r="D56" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="E56">
-        <v>800</v>
-      </c>
-      <c r="F56">
-        <v>1</v>
-      </c>
-      <c r="G56">
+      <c r="E56" s="3">
+        <v>800</v>
+      </c>
+      <c r="F56" s="3">
+        <v>1</v>
+      </c>
+      <c r="G56" s="3">
         <v>500</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B57" s="1">
+      <c r="B57" s="2">
         <v>1001104</v>
       </c>
-      <c r="C57" s="1" t="s">
+      <c r="C57" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="D57" s="5" t="s">
+      <c r="D57" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="E57">
-        <v>900</v>
-      </c>
-      <c r="F57">
+      <c r="E57" s="3">
+        <v>900</v>
+      </c>
+      <c r="F57" s="3">
         <v>2</v>
       </c>
-      <c r="G57">
+      <c r="G57" s="3">
         <v>150</v>
       </c>
-      <c r="H57">
+      <c r="H57" s="3">
         <v>733</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B58" s="1">
+      <c r="B58" s="2">
         <v>1001105</v>
       </c>
-      <c r="C58" s="1" t="s">
+      <c r="C58" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="D58" t="s">
+      <c r="D58" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="E58">
-        <v>900</v>
-      </c>
-      <c r="F58">
-        <v>1</v>
-      </c>
-      <c r="G58">
+      <c r="E58" s="3">
+        <v>900</v>
+      </c>
+      <c r="F58" s="3">
+        <v>1</v>
+      </c>
+      <c r="G58" s="3">
         <v>450</v>
       </c>
-      <c r="H58">
+      <c r="H58" s="3">
         <v>900</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B59" s="1">
+      <c r="B59" s="2">
         <v>1001201</v>
       </c>
-      <c r="C59" s="1" t="s">
+      <c r="C59" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="D59" t="s">
+      <c r="D59" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="E59">
-        <v>500</v>
-      </c>
-      <c r="F59">
+      <c r="E59" s="3">
+        <v>500</v>
+      </c>
+      <c r="F59" s="3">
         <v>0.85</v>
       </c>
-      <c r="G59">
+      <c r="G59" s="3">
         <v>319</v>
       </c>
-      <c r="H59">
+      <c r="H59" s="3">
         <v>319</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B60" s="1">
+      <c r="B60" s="2">
         <v>1001202</v>
       </c>
-      <c r="C60" s="1" t="s">
+      <c r="C60" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="D60" t="s">
+      <c r="D60" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="E60">
-        <v>900</v>
-      </c>
-      <c r="F60">
+      <c r="E60" s="3">
+        <v>900</v>
+      </c>
+      <c r="F60" s="3">
         <v>1.2</v>
       </c>
-      <c r="G60">
+      <c r="G60" s="3">
         <v>400</v>
       </c>
-      <c r="H60">
+      <c r="H60" s="3">
         <v>720</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B61" s="1">
+      <c r="B61" s="2">
         <v>1001203</v>
       </c>
-      <c r="C61" s="1" t="s">
+      <c r="C61" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="D61" t="s">
+      <c r="D61" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="E61">
-        <v>800</v>
-      </c>
-      <c r="F61">
-        <v>1</v>
-      </c>
-      <c r="G61">
+      <c r="E61" s="3">
+        <v>800</v>
+      </c>
+      <c r="F61" s="3">
+        <v>1</v>
+      </c>
+      <c r="G61" s="3">
         <v>500</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B62" s="1">
+      <c r="B62" s="2">
         <v>1001204</v>
       </c>
-      <c r="C62" s="1" t="s">
+      <c r="C62" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="D62" t="s">
+      <c r="D62" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="E62">
-        <v>900</v>
-      </c>
-      <c r="F62">
+      <c r="E62" s="3">
+        <v>900</v>
+      </c>
+      <c r="F62" s="3">
         <v>2</v>
       </c>
-      <c r="G62">
+      <c r="G62" s="3">
         <v>150</v>
       </c>
-      <c r="H62">
+      <c r="H62" s="3">
         <v>733</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B63" s="1">
+      <c r="B63" s="2">
         <v>1001205</v>
       </c>
-      <c r="C63" s="1" t="s">
+      <c r="C63" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="D63" t="s">
+      <c r="D63" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="E63">
-        <v>900</v>
-      </c>
-      <c r="F63">
-        <v>1</v>
-      </c>
-      <c r="G63">
+      <c r="E63" s="3">
+        <v>900</v>
+      </c>
+      <c r="F63" s="3">
+        <v>1</v>
+      </c>
+      <c r="G63" s="3">
         <v>450</v>
       </c>
-      <c r="H63">
+      <c r="H63" s="3">
         <v>900</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B64" s="6">
+      <c r="B64" s="2">
         <v>1001301</v>
       </c>
-      <c r="C64" s="6" t="s">
+      <c r="C64" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="D64" s="7" t="s">
+      <c r="D64" s="4" t="s">
         <v>53</v>
       </c>
       <c r="E64" s="3">
@@ -2161,13 +2157,13 @@
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B65" s="6">
+      <c r="B65" s="2">
         <v>1001302</v>
       </c>
-      <c r="C65" s="6" t="s">
+      <c r="C65" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="D65" s="7" t="s">
+      <c r="D65" s="4" t="s">
         <v>53</v>
       </c>
       <c r="E65" s="3">
@@ -2184,13 +2180,13 @@
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B66" s="6">
+      <c r="B66" s="2">
         <v>1001303</v>
       </c>
-      <c r="C66" s="6" t="s">
+      <c r="C66" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="D66" s="7" t="s">
+      <c r="D66" s="4" t="s">
         <v>53</v>
       </c>
       <c r="E66" s="3">
@@ -2202,16 +2198,15 @@
       <c r="G66" s="3">
         <v>500</v>
       </c>
-      <c r="H66" s="3"/>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B67" s="6">
+      <c r="B67" s="2">
         <v>1001304</v>
       </c>
-      <c r="C67" s="6" t="s">
+      <c r="C67" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="D67" s="7" t="s">
+      <c r="D67" s="4" t="s">
         <v>53</v>
       </c>
       <c r="E67" s="3">
@@ -2228,13 +2223,13 @@
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B68" s="6">
+      <c r="B68" s="2">
         <v>1001305</v>
       </c>
-      <c r="C68" s="6" t="s">
+      <c r="C68" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="D68" s="7" t="s">
+      <c r="D68" s="4" t="s">
         <v>53</v>
       </c>
       <c r="E68" s="3">
@@ -2251,583 +2246,583 @@
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A69" s="1"/>
-      <c r="B69" s="1">
+      <c r="A69" s="2"/>
+      <c r="B69" s="2">
         <v>1001401</v>
       </c>
-      <c r="C69" s="1" t="s">
+      <c r="C69" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="D69" t="s">
+      <c r="D69" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="E69">
+      <c r="E69" s="3">
         <v>460</v>
       </c>
-      <c r="F69">
+      <c r="F69" s="3">
         <v>0.94</v>
       </c>
-      <c r="G69">
+      <c r="G69" s="3">
         <v>319</v>
       </c>
-      <c r="H69">
+      <c r="H69" s="3">
         <v>319</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A70" s="1"/>
-      <c r="B70" s="1">
+      <c r="A70" s="2"/>
+      <c r="B70" s="2">
         <v>1001402</v>
       </c>
-      <c r="C70" s="1" t="s">
+      <c r="C70" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="D70" t="s">
+      <c r="D70" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="E70">
+      <c r="E70" s="3">
         <v>1615</v>
       </c>
-      <c r="F70">
+      <c r="F70" s="3">
         <v>2</v>
       </c>
-      <c r="G70">
+      <c r="G70" s="3">
         <v>550</v>
       </c>
-      <c r="H70">
+      <c r="H70" s="3">
         <v>1300</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A71" s="1"/>
-      <c r="B71" s="1">
+      <c r="A71" s="2"/>
+      <c r="B71" s="2">
         <v>1001403</v>
       </c>
-      <c r="C71" s="1" t="s">
+      <c r="C71" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="D71" t="s">
+      <c r="D71" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="E71">
-        <v>800</v>
-      </c>
-      <c r="F71">
-        <v>1</v>
-      </c>
-      <c r="G71">
+      <c r="E71" s="3">
+        <v>800</v>
+      </c>
+      <c r="F71" s="3">
+        <v>1</v>
+      </c>
+      <c r="G71" s="3">
         <v>500</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A72" s="1"/>
-      <c r="B72" s="1">
+      <c r="A72" s="2"/>
+      <c r="B72" s="2">
         <v>1001404</v>
       </c>
-      <c r="C72" s="1" t="s">
+      <c r="C72" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="D72" t="s">
+      <c r="D72" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="E72">
-        <v>900</v>
-      </c>
-      <c r="F72">
+      <c r="E72" s="3">
+        <v>900</v>
+      </c>
+      <c r="F72" s="3">
         <v>2</v>
       </c>
-      <c r="G72">
+      <c r="G72" s="3">
         <v>150</v>
       </c>
-      <c r="H72">
+      <c r="H72" s="3">
         <v>733</v>
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A73" s="1"/>
-      <c r="B73" s="1">
+      <c r="A73" s="2"/>
+      <c r="B73" s="2">
         <v>1001405</v>
       </c>
-      <c r="C73" s="1" t="s">
+      <c r="C73" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="D73" t="s">
+      <c r="D73" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="E73">
-        <v>900</v>
-      </c>
-      <c r="F73">
-        <v>1</v>
-      </c>
-      <c r="G73">
+      <c r="E73" s="3">
+        <v>900</v>
+      </c>
+      <c r="F73" s="3">
+        <v>1</v>
+      </c>
+      <c r="G73" s="3">
         <v>450</v>
       </c>
-      <c r="H73">
+      <c r="H73" s="3">
         <v>900</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A74" s="1"/>
-      <c r="B74" s="1">
+      <c r="A74" s="2"/>
+      <c r="B74" s="2">
         <v>1001501</v>
       </c>
-      <c r="C74" s="1" t="s">
+      <c r="C74" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="D74" s="5" t="s">
+      <c r="D74" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="E74">
-        <v>500</v>
-      </c>
-      <c r="F74">
+      <c r="E74" s="3">
+        <v>500</v>
+      </c>
+      <c r="F74" s="3">
         <v>0.85</v>
       </c>
-      <c r="G74">
+      <c r="G74" s="3">
         <v>319</v>
       </c>
-      <c r="H74">
+      <c r="H74" s="3">
         <v>319</v>
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A75" s="1"/>
-      <c r="B75" s="1">
+      <c r="A75" s="2"/>
+      <c r="B75" s="2">
         <v>1001502</v>
       </c>
-      <c r="C75" s="1" t="s">
+      <c r="C75" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="D75" s="5" t="s">
+      <c r="D75" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="E75">
-        <v>900</v>
-      </c>
-      <c r="F75">
+      <c r="E75" s="3">
+        <v>900</v>
+      </c>
+      <c r="F75" s="3">
         <v>1.2</v>
       </c>
-      <c r="G75">
+      <c r="G75" s="3">
         <v>400</v>
       </c>
-      <c r="H75">
+      <c r="H75" s="3">
         <v>720</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A76" s="1"/>
-      <c r="B76" s="1">
+      <c r="A76" s="2"/>
+      <c r="B76" s="2">
         <v>1001503</v>
       </c>
-      <c r="C76" s="1" t="s">
+      <c r="C76" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="D76" s="5" t="s">
+      <c r="D76" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="E76">
-        <v>800</v>
-      </c>
-      <c r="F76">
-        <v>1</v>
-      </c>
-      <c r="G76">
+      <c r="E76" s="3">
+        <v>800</v>
+      </c>
+      <c r="F76" s="3">
+        <v>1</v>
+      </c>
+      <c r="G76" s="3">
         <v>500</v>
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A77" s="1"/>
-      <c r="B77" s="1">
+      <c r="A77" s="2"/>
+      <c r="B77" s="2">
         <v>1001504</v>
       </c>
-      <c r="C77" s="1" t="s">
+      <c r="C77" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="D77" s="5" t="s">
+      <c r="D77" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="E77">
-        <v>900</v>
-      </c>
-      <c r="F77">
+      <c r="E77" s="3">
+        <v>900</v>
+      </c>
+      <c r="F77" s="3">
         <v>2</v>
       </c>
-      <c r="G77">
+      <c r="G77" s="3">
         <v>150</v>
       </c>
-      <c r="H77">
+      <c r="H77" s="3">
         <v>733</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A78" s="1"/>
-      <c r="B78" s="1">
+      <c r="A78" s="2"/>
+      <c r="B78" s="2">
         <v>1001505</v>
       </c>
-      <c r="C78" s="1" t="s">
+      <c r="C78" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="D78" s="5" t="s">
+      <c r="D78" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="E78">
-        <v>900</v>
-      </c>
-      <c r="F78">
-        <v>1</v>
-      </c>
-      <c r="G78">
+      <c r="E78" s="3">
+        <v>900</v>
+      </c>
+      <c r="F78" s="3">
+        <v>1</v>
+      </c>
+      <c r="G78" s="3">
         <v>450</v>
       </c>
-      <c r="H78">
+      <c r="H78" s="3">
         <v>900</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B79" s="1">
+      <c r="B79" s="2">
         <v>1001601</v>
       </c>
-      <c r="C79" s="1" t="s">
+      <c r="C79" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="D79" s="5" t="s">
+      <c r="D79" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="E79">
+      <c r="E79" s="3">
         <v>460</v>
       </c>
-      <c r="F79">
+      <c r="F79" s="3">
         <v>0.94</v>
       </c>
-      <c r="G79">
+      <c r="G79" s="3">
         <v>319</v>
       </c>
-      <c r="H79">
+      <c r="H79" s="3">
         <v>319</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B80" s="1">
+      <c r="B80" s="2">
         <v>1001602</v>
       </c>
-      <c r="C80" s="1" t="s">
+      <c r="C80" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="D80" s="5" t="s">
+      <c r="D80" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="E80">
+      <c r="E80" s="3">
         <v>1615</v>
       </c>
-      <c r="F80">
+      <c r="F80" s="3">
         <v>2</v>
       </c>
-      <c r="G80">
+      <c r="G80" s="3">
         <v>550</v>
       </c>
-      <c r="H80">
+      <c r="H80" s="3">
         <v>1300</v>
       </c>
     </row>
     <row r="81" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B81" s="1">
+      <c r="B81" s="2">
         <v>1001603</v>
       </c>
-      <c r="C81" s="1" t="s">
+      <c r="C81" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="D81" s="5" t="s">
+      <c r="D81" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="E81">
-        <v>800</v>
-      </c>
-      <c r="F81">
-        <v>1</v>
-      </c>
-      <c r="G81">
+      <c r="E81" s="3">
+        <v>800</v>
+      </c>
+      <c r="F81" s="3">
+        <v>1</v>
+      </c>
+      <c r="G81" s="3">
         <v>500</v>
       </c>
     </row>
     <row r="82" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B82" s="1">
+      <c r="B82" s="2">
         <v>1001604</v>
       </c>
-      <c r="C82" s="1" t="s">
+      <c r="C82" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="D82" s="5" t="s">
+      <c r="D82" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="E82">
-        <v>900</v>
-      </c>
-      <c r="F82">
+      <c r="E82" s="3">
+        <v>900</v>
+      </c>
+      <c r="F82" s="3">
         <v>2</v>
       </c>
-      <c r="G82">
+      <c r="G82" s="3">
         <v>150</v>
       </c>
-      <c r="H82">
+      <c r="H82" s="3">
         <v>733</v>
       </c>
     </row>
     <row r="83" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B83" s="1">
+      <c r="B83" s="2">
         <v>1001605</v>
       </c>
-      <c r="C83" s="1" t="s">
+      <c r="C83" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="D83" s="5" t="s">
+      <c r="D83" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="E83">
-        <v>900</v>
-      </c>
-      <c r="F83">
-        <v>1</v>
-      </c>
-      <c r="G83">
+      <c r="E83" s="3">
+        <v>900</v>
+      </c>
+      <c r="F83" s="3">
+        <v>1</v>
+      </c>
+      <c r="G83" s="3">
         <v>450</v>
       </c>
-      <c r="H83">
+      <c r="H83" s="3">
         <v>900</v>
       </c>
     </row>
     <row r="84" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B84" s="1">
+      <c r="B84" s="2">
         <v>1001701</v>
       </c>
-      <c r="C84" s="1" t="s">
+      <c r="C84" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="D84" s="5" t="s">
+      <c r="D84" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="E84">
+      <c r="E84" s="3">
         <v>460</v>
       </c>
-      <c r="F84">
+      <c r="F84" s="3">
         <v>0.94</v>
       </c>
-      <c r="G84">
+      <c r="G84" s="3">
         <v>319</v>
       </c>
-      <c r="H84">
+      <c r="H84" s="3">
         <v>319</v>
       </c>
     </row>
     <row r="85" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B85" s="1">
+      <c r="B85" s="2">
         <v>1001702</v>
       </c>
-      <c r="C85" s="1" t="s">
+      <c r="C85" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="D85" s="5" t="s">
+      <c r="D85" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="E85">
+      <c r="E85" s="3">
         <v>1615</v>
       </c>
-      <c r="F85">
+      <c r="F85" s="3">
         <v>2</v>
       </c>
-      <c r="G85">
+      <c r="G85" s="3">
         <v>550</v>
       </c>
-      <c r="H85">
+      <c r="H85" s="3">
         <v>1300</v>
       </c>
     </row>
     <row r="86" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B86" s="1">
+      <c r="B86" s="2">
         <v>1001703</v>
       </c>
-      <c r="C86" s="1" t="s">
+      <c r="C86" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="D86" s="5" t="s">
+      <c r="D86" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="E86">
-        <v>800</v>
-      </c>
-      <c r="F86">
-        <v>1</v>
-      </c>
-      <c r="G86">
+      <c r="E86" s="3">
+        <v>800</v>
+      </c>
+      <c r="F86" s="3">
+        <v>1</v>
+      </c>
+      <c r="G86" s="3">
         <v>500</v>
       </c>
     </row>
     <row r="87" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B87" s="1">
+      <c r="B87" s="2">
         <v>1001704</v>
       </c>
-      <c r="C87" s="1" t="s">
+      <c r="C87" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="D87" s="5" t="s">
+      <c r="D87" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="E87">
-        <v>900</v>
-      </c>
-      <c r="F87">
+      <c r="E87" s="3">
+        <v>900</v>
+      </c>
+      <c r="F87" s="3">
         <v>2</v>
       </c>
-      <c r="G87">
+      <c r="G87" s="3">
         <v>150</v>
       </c>
-      <c r="H87">
+      <c r="H87" s="3">
         <v>733</v>
       </c>
     </row>
     <row r="88" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B88" s="1">
+      <c r="B88" s="2">
         <v>1001705</v>
       </c>
-      <c r="C88" s="1" t="s">
+      <c r="C88" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="D88" s="5" t="s">
+      <c r="D88" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="E88">
-        <v>900</v>
-      </c>
-      <c r="F88">
-        <v>1</v>
-      </c>
-      <c r="G88">
+      <c r="E88" s="3">
+        <v>900</v>
+      </c>
+      <c r="F88" s="3">
+        <v>1</v>
+      </c>
+      <c r="G88" s="3">
         <v>450</v>
       </c>
-      <c r="H88">
+      <c r="H88" s="3">
         <v>900</v>
       </c>
     </row>
     <row r="89" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B89" s="1">
+      <c r="B89" s="2">
         <v>1001801</v>
       </c>
-      <c r="C89" s="1" t="s">
+      <c r="C89" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="D89" s="5" t="s">
+      <c r="D89" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="E89">
+      <c r="E89" s="3">
         <v>460</v>
       </c>
-      <c r="F89">
+      <c r="F89" s="3">
         <v>0.94</v>
       </c>
-      <c r="G89">
+      <c r="G89" s="3">
         <v>319</v>
       </c>
-      <c r="H89">
+      <c r="H89" s="3">
         <v>319</v>
       </c>
     </row>
     <row r="90" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B90" s="1">
+      <c r="B90" s="2">
         <v>1001802</v>
       </c>
-      <c r="C90" s="1" t="s">
+      <c r="C90" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="D90" s="5" t="s">
+      <c r="D90" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="E90">
+      <c r="E90" s="3">
         <v>1615</v>
       </c>
-      <c r="F90">
+      <c r="F90" s="3">
         <v>2</v>
       </c>
-      <c r="G90">
+      <c r="G90" s="3">
         <v>550</v>
       </c>
-      <c r="H90">
+      <c r="H90" s="3">
         <v>1300</v>
       </c>
     </row>
     <row r="91" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B91" s="1">
+      <c r="B91" s="2">
         <v>1001803</v>
       </c>
-      <c r="C91" s="1" t="s">
+      <c r="C91" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="D91" s="5" t="s">
+      <c r="D91" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="E91">
-        <v>800</v>
-      </c>
-      <c r="F91">
-        <v>1</v>
-      </c>
-      <c r="G91">
+      <c r="E91" s="3">
+        <v>800</v>
+      </c>
+      <c r="F91" s="3">
+        <v>1</v>
+      </c>
+      <c r="G91" s="3">
         <v>500</v>
       </c>
     </row>
     <row r="92" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B92" s="1">
+      <c r="B92" s="2">
         <v>1001804</v>
       </c>
-      <c r="C92" s="1" t="s">
+      <c r="C92" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="D92" s="5" t="s">
+      <c r="D92" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="E92">
-        <v>900</v>
-      </c>
-      <c r="F92">
+      <c r="E92" s="3">
+        <v>900</v>
+      </c>
+      <c r="F92" s="3">
         <v>2</v>
       </c>
-      <c r="G92">
+      <c r="G92" s="3">
         <v>150</v>
       </c>
-      <c r="H92">
+      <c r="H92" s="3">
         <v>733</v>
       </c>
     </row>
     <row r="93" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B93" s="1">
+      <c r="B93" s="2">
         <v>1001805</v>
       </c>
-      <c r="C93" s="1" t="s">
+      <c r="C93" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="D93" s="5" t="s">
+      <c r="D93" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="E93">
-        <v>900</v>
-      </c>
-      <c r="F93">
-        <v>1</v>
-      </c>
-      <c r="G93">
+      <c r="E93" s="3">
+        <v>900</v>
+      </c>
+      <c r="F93" s="3">
+        <v>1</v>
+      </c>
+      <c r="G93" s="3">
         <v>450</v>
       </c>
-      <c r="H93">
+      <c r="H93" s="3">
         <v>900</v>
       </c>
     </row>
     <row r="94" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B94" s="1">
+      <c r="B94" s="2">
         <v>1001901</v>
       </c>
-      <c r="C94" s="1" t="s">
+      <c r="C94" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="D94" s="5" t="s">
+      <c r="D94" s="4" t="s">
         <v>61</v>
       </c>
       <c r="E94" s="3">
@@ -2844,13 +2839,13 @@
       </c>
     </row>
     <row r="95" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B95" s="1">
+      <c r="B95" s="2">
         <v>1001902</v>
       </c>
-      <c r="C95" s="1" t="s">
+      <c r="C95" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="D95" s="5" t="s">
+      <c r="D95" s="4" t="s">
         <v>61</v>
       </c>
       <c r="E95" s="3">
@@ -2867,13 +2862,13 @@
       </c>
     </row>
     <row r="96" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B96" s="1">
+      <c r="B96" s="2">
         <v>1001903</v>
       </c>
-      <c r="C96" s="1" t="s">
+      <c r="C96" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="D96" s="5" t="s">
+      <c r="D96" s="4" t="s">
         <v>61</v>
       </c>
       <c r="E96" s="3">
@@ -2885,16 +2880,15 @@
       <c r="G96" s="3">
         <v>500</v>
       </c>
-      <c r="H96" s="3"/>
-    </row>
-    <row r="97" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B97" s="1">
+    </row>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B97" s="2">
         <v>1001904</v>
       </c>
-      <c r="C97" s="1" t="s">
+      <c r="C97" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="D97" s="5" t="s">
+      <c r="D97" s="4" t="s">
         <v>61</v>
       </c>
       <c r="E97" s="3">
@@ -2910,14 +2904,14 @@
         <v>325</v>
       </c>
     </row>
-    <row r="98" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B98" s="1">
+    <row r="98" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B98" s="2">
         <v>1001905</v>
       </c>
-      <c r="C98" s="1" t="s">
+      <c r="C98" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="D98" s="5" t="s">
+      <c r="D98" s="4" t="s">
         <v>61</v>
       </c>
       <c r="E98" s="3">
@@ -2930,6 +2924,474 @@
         <v>520</v>
       </c>
       <c r="H98" s="3">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A99" s="2"/>
+      <c r="B99" s="2">
+        <v>1002001</v>
+      </c>
+      <c r="C99" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D99" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="E99" s="3">
+        <v>800</v>
+      </c>
+      <c r="F99" s="3">
+        <v>1.5</v>
+      </c>
+      <c r="G99" s="3">
+        <v>650</v>
+      </c>
+      <c r="H99" s="3">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A100" s="2"/>
+      <c r="B100" s="2">
+        <v>1002002</v>
+      </c>
+      <c r="C100" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D100" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="E100" s="3">
+        <v>900</v>
+      </c>
+      <c r="F100" s="3">
+        <v>1</v>
+      </c>
+      <c r="G100" s="3">
+        <v>270</v>
+      </c>
+      <c r="H100" s="3">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A101" s="2"/>
+      <c r="B101" s="2">
+        <v>1002003</v>
+      </c>
+      <c r="C101" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D101" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="E101" s="3">
+        <v>800</v>
+      </c>
+      <c r="F101" s="3">
+        <v>1</v>
+      </c>
+      <c r="G101" s="3">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A102" s="2"/>
+      <c r="B102" s="2">
+        <v>1002004</v>
+      </c>
+      <c r="C102" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D102" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="E102" s="3">
+        <v>500</v>
+      </c>
+      <c r="F102" s="3">
+        <v>1</v>
+      </c>
+      <c r="G102" s="3">
+        <v>100</v>
+      </c>
+      <c r="H102" s="3">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A103" s="2"/>
+      <c r="B103" s="2">
+        <v>1002005</v>
+      </c>
+      <c r="C103" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D103" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="E103" s="3">
+        <v>833</v>
+      </c>
+      <c r="F103" s="3">
+        <v>1</v>
+      </c>
+      <c r="G103" s="3">
+        <v>520</v>
+      </c>
+      <c r="H103" s="3">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="104" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A104" s="2"/>
+      <c r="B104" s="2">
+        <v>1002101</v>
+      </c>
+      <c r="C104" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D104" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="E104" s="3">
+        <v>800</v>
+      </c>
+      <c r="F104" s="3">
+        <v>1.5</v>
+      </c>
+      <c r="G104" s="3">
+        <v>650</v>
+      </c>
+      <c r="H104" s="3">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="105" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A105" s="2"/>
+      <c r="B105" s="2">
+        <v>1002102</v>
+      </c>
+      <c r="C105" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D105" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="E105" s="3">
+        <v>900</v>
+      </c>
+      <c r="F105" s="3">
+        <v>1</v>
+      </c>
+      <c r="G105" s="3">
+        <v>270</v>
+      </c>
+      <c r="H105" s="3">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="106" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A106" s="2"/>
+      <c r="B106" s="2">
+        <v>1002103</v>
+      </c>
+      <c r="C106" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D106" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="E106" s="3">
+        <v>800</v>
+      </c>
+      <c r="F106" s="3">
+        <v>1</v>
+      </c>
+      <c r="G106" s="3">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="107" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A107" s="2"/>
+      <c r="B107" s="2">
+        <v>1002104</v>
+      </c>
+      <c r="C107" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D107" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="E107" s="3">
+        <v>500</v>
+      </c>
+      <c r="F107" s="3">
+        <v>1</v>
+      </c>
+      <c r="G107" s="3">
+        <v>100</v>
+      </c>
+      <c r="H107" s="3">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A108" s="2"/>
+      <c r="B108" s="2">
+        <v>1002105</v>
+      </c>
+      <c r="C108" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D108" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="E108" s="3">
+        <v>833</v>
+      </c>
+      <c r="F108" s="3">
+        <v>1</v>
+      </c>
+      <c r="G108" s="3">
+        <v>520</v>
+      </c>
+      <c r="H108" s="3">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="109" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A109" s="2"/>
+      <c r="B109" s="2">
+        <v>1002201</v>
+      </c>
+      <c r="C109" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D109" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E109" s="3">
+        <v>800</v>
+      </c>
+      <c r="F109" s="3">
+        <v>1.5</v>
+      </c>
+      <c r="G109" s="3">
+        <v>650</v>
+      </c>
+      <c r="H109" s="3">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="110" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A110" s="2"/>
+      <c r="B110" s="2">
+        <v>1002202</v>
+      </c>
+      <c r="C110" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D110" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E110" s="3">
+        <v>900</v>
+      </c>
+      <c r="F110" s="3">
+        <v>1</v>
+      </c>
+      <c r="G110" s="3">
+        <v>270</v>
+      </c>
+      <c r="H110" s="3">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="111" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A111" s="2"/>
+      <c r="B111" s="2">
+        <v>1002203</v>
+      </c>
+      <c r="C111" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D111" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E111" s="3">
+        <v>800</v>
+      </c>
+      <c r="F111" s="3">
+        <v>1</v>
+      </c>
+      <c r="G111" s="3">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="112" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A112" s="2"/>
+      <c r="B112" s="2">
+        <v>1002204</v>
+      </c>
+      <c r="C112" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D112" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E112" s="3">
+        <v>500</v>
+      </c>
+      <c r="F112" s="3">
+        <v>1</v>
+      </c>
+      <c r="G112" s="3">
+        <v>100</v>
+      </c>
+      <c r="H112" s="3">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="113" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A113" s="2"/>
+      <c r="B113" s="2">
+        <v>1002205</v>
+      </c>
+      <c r="C113" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D113" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E113" s="3">
+        <v>833</v>
+      </c>
+      <c r="F113" s="3">
+        <v>1</v>
+      </c>
+      <c r="G113" s="3">
+        <v>520</v>
+      </c>
+      <c r="H113" s="3">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="114" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A114" s="2"/>
+      <c r="B114" s="2">
+        <v>1002301</v>
+      </c>
+      <c r="C114" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D114" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="E114" s="3">
+        <v>800</v>
+      </c>
+      <c r="F114" s="3">
+        <v>1.5</v>
+      </c>
+      <c r="G114" s="3">
+        <v>650</v>
+      </c>
+      <c r="H114" s="3">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="115" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A115" s="2"/>
+      <c r="B115" s="2">
+        <v>1002302</v>
+      </c>
+      <c r="C115" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D115" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="E115" s="3">
+        <v>900</v>
+      </c>
+      <c r="F115" s="3">
+        <v>1</v>
+      </c>
+      <c r="G115" s="3">
+        <v>270</v>
+      </c>
+      <c r="H115" s="3">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="116" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A116" s="2"/>
+      <c r="B116" s="2">
+        <v>1002303</v>
+      </c>
+      <c r="C116" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D116" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="E116" s="3">
+        <v>800</v>
+      </c>
+      <c r="F116" s="3">
+        <v>1</v>
+      </c>
+      <c r="G116" s="3">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="117" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A117" s="2"/>
+      <c r="B117" s="2">
+        <v>1002304</v>
+      </c>
+      <c r="C117" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D117" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="E117" s="3">
+        <v>500</v>
+      </c>
+      <c r="F117" s="3">
+        <v>1</v>
+      </c>
+      <c r="G117" s="3">
+        <v>100</v>
+      </c>
+      <c r="H117" s="3">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="118" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A118" s="2"/>
+      <c r="B118" s="2">
+        <v>1002305</v>
+      </c>
+      <c r="C118" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D118" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="E118" s="3">
+        <v>833</v>
+      </c>
+      <c r="F118" s="3">
+        <v>1</v>
+      </c>
+      <c r="G118" s="3">
+        <v>520</v>
+      </c>
+      <c r="H118" s="3">
         <v>800</v>
       </c>
     </row>

--- a/source/bin/excel/animation.xlsx
+++ b/source/bin/excel/animation.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\liqi-excel\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22998945-3C76-4E64-AE41-136D0C95FF2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{725A2B75-9961-4974-9DA0-222D8F9FC993}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="329" uniqueCount="70">
   <si>
     <t>sheet</t>
   </si>
@@ -255,6 +255,22 @@
   </si>
   <si>
     <t>hand_banbenchenma</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>hand_tongren</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>hand_yasina</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>hand_shinai</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>hand_lifa</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -313,17 +329,26 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="1">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -635,2764 +660,3211 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:O118"/>
+  <dimension ref="A1:O138"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="13.375" style="3" customWidth="1"/>
-    <col min="2" max="3" width="12" style="3" customWidth="1"/>
-    <col min="4" max="4" width="20" style="3" customWidth="1"/>
-    <col min="5" max="5" width="26.625" style="3" customWidth="1"/>
-    <col min="6" max="6" width="21" style="3" customWidth="1"/>
-    <col min="7" max="15" width="12.75" style="3" customWidth="1"/>
-    <col min="16" max="16" width="10.375" style="3" customWidth="1"/>
-    <col min="17" max="17" width="9.125" style="3" customWidth="1"/>
-    <col min="18" max="18" width="9" style="3" customWidth="1"/>
-    <col min="19" max="19" width="10.375" style="3" customWidth="1"/>
-    <col min="20" max="20" width="13" style="3" customWidth="1"/>
-    <col min="21" max="21" width="5.5" style="3" customWidth="1"/>
-    <col min="22" max="22" width="12.625" style="3" customWidth="1"/>
-    <col min="23" max="23" width="13" style="3" customWidth="1"/>
-    <col min="24" max="16384" width="9" style="3"/>
+    <col min="1" max="1" width="13.375" customWidth="1"/>
+    <col min="2" max="3" width="12" customWidth="1"/>
+    <col min="4" max="4" width="20" customWidth="1"/>
+    <col min="5" max="5" width="26.625" customWidth="1"/>
+    <col min="6" max="6" width="21" customWidth="1"/>
+    <col min="7" max="15" width="12.75" customWidth="1"/>
+    <col min="16" max="16" width="10.375" customWidth="1"/>
+    <col min="17" max="17" width="9.125" customWidth="1"/>
+    <col min="18" max="18" width="9" customWidth="1"/>
+    <col min="19" max="19" width="10.375" customWidth="1"/>
+    <col min="20" max="20" width="13" customWidth="1"/>
+    <col min="21" max="21" width="5.5" customWidth="1"/>
+    <col min="22" max="22" width="12.625" customWidth="1"/>
+    <col min="23" max="23" width="13" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="L1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="M1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="N1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="O1" s="1" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="E2" s="3" t="s">
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="E2" t="s">
         <v>21</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G2" s="1" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" t="s">
         <v>26</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" t="s">
         <v>25</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="G3" s="1" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A4" s="2"/>
-      <c r="B4" s="2">
+      <c r="A4" s="1"/>
+      <c r="B4" s="1">
         <v>1000101</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" t="s">
         <v>29</v>
       </c>
-      <c r="E4" s="3">
+      <c r="E4">
         <v>460</v>
       </c>
-      <c r="F4" s="3">
+      <c r="F4">
         <v>0.94</v>
       </c>
-      <c r="G4" s="3">
+      <c r="G4">
         <v>319</v>
       </c>
-      <c r="H4" s="3">
+      <c r="H4">
         <v>319</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A5" s="2"/>
-      <c r="B5" s="2">
+      <c r="A5" s="1"/>
+      <c r="B5" s="1">
         <v>1000102</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D5" t="s">
         <v>29</v>
       </c>
-      <c r="E5" s="3">
+      <c r="E5">
         <v>1615</v>
       </c>
-      <c r="F5" s="3">
+      <c r="F5">
         <v>2</v>
       </c>
-      <c r="G5" s="3">
+      <c r="G5">
         <v>550</v>
       </c>
-      <c r="H5" s="3">
+      <c r="H5">
         <v>1300</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A6" s="2"/>
-      <c r="B6" s="2">
+      <c r="A6" s="1"/>
+      <c r="B6" s="1">
         <v>1000103</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="D6" t="s">
         <v>29</v>
       </c>
-      <c r="E6" s="3">
-        <v>800</v>
-      </c>
-      <c r="F6" s="3">
-        <v>1</v>
-      </c>
-      <c r="G6" s="3">
+      <c r="E6">
+        <v>800</v>
+      </c>
+      <c r="F6">
+        <v>1</v>
+      </c>
+      <c r="G6">
         <v>500</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A7" s="2"/>
-      <c r="B7" s="2">
+      <c r="A7" s="1"/>
+      <c r="B7" s="1">
         <v>1000104</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="D7" t="s">
         <v>29</v>
       </c>
-      <c r="E7" s="3">
-        <v>900</v>
-      </c>
-      <c r="F7" s="3">
+      <c r="E7">
+        <v>900</v>
+      </c>
+      <c r="F7">
         <v>2</v>
       </c>
-      <c r="G7" s="3">
+      <c r="G7">
         <v>150</v>
       </c>
-      <c r="H7" s="3">
+      <c r="H7">
         <v>733</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A8" s="2"/>
-      <c r="B8" s="2">
+      <c r="A8" s="1"/>
+      <c r="B8" s="1">
         <v>1000105</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C8" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="D8" s="3" t="s">
+      <c r="D8" t="s">
         <v>29</v>
       </c>
-      <c r="E8" s="3">
-        <v>900</v>
-      </c>
-      <c r="F8" s="3">
-        <v>1</v>
-      </c>
-      <c r="G8" s="3">
+      <c r="E8">
+        <v>900</v>
+      </c>
+      <c r="F8">
+        <v>1</v>
+      </c>
+      <c r="G8">
         <v>450</v>
       </c>
-      <c r="H8" s="3">
+      <c r="H8">
         <v>900</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A9" s="2"/>
-      <c r="B9" s="2">
+      <c r="A9" s="1"/>
+      <c r="B9" s="1">
         <v>1000201</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="C9" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D9" s="3" t="s">
+      <c r="D9" t="s">
         <v>34</v>
       </c>
-      <c r="E9" s="3">
-        <v>500</v>
-      </c>
-      <c r="F9" s="3">
+      <c r="E9">
+        <v>500</v>
+      </c>
+      <c r="F9">
         <v>0.85</v>
       </c>
-      <c r="G9" s="3">
+      <c r="G9">
         <v>319</v>
       </c>
-      <c r="H9" s="3">
+      <c r="H9">
         <v>319</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A10" s="2"/>
-      <c r="B10" s="2">
+      <c r="A10" s="1"/>
+      <c r="B10" s="1">
         <v>1000202</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="C10" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D10" s="3" t="s">
+      <c r="D10" t="s">
         <v>34</v>
       </c>
-      <c r="E10" s="3">
-        <v>900</v>
-      </c>
-      <c r="F10" s="3">
+      <c r="E10">
+        <v>900</v>
+      </c>
+      <c r="F10">
         <v>1.2</v>
       </c>
-      <c r="G10" s="3">
+      <c r="G10">
         <v>400</v>
       </c>
-      <c r="H10" s="3">
+      <c r="H10">
         <v>720</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A11" s="2"/>
-      <c r="B11" s="2">
+      <c r="A11" s="1"/>
+      <c r="B11" s="1">
         <v>1000203</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="C11" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="D11" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="E11" s="3">
-        <v>800</v>
-      </c>
-      <c r="F11" s="3">
-        <v>1</v>
-      </c>
-      <c r="G11" s="3">
+      <c r="E11">
+        <v>800</v>
+      </c>
+      <c r="F11">
+        <v>1</v>
+      </c>
+      <c r="G11">
         <v>500</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A12" s="2"/>
-      <c r="B12" s="2">
+      <c r="A12" s="1"/>
+      <c r="B12" s="1">
         <v>1000204</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="C12" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D12" s="3" t="s">
+      <c r="D12" t="s">
         <v>34</v>
       </c>
-      <c r="E12" s="3">
-        <v>900</v>
-      </c>
-      <c r="F12" s="3">
+      <c r="E12">
+        <v>900</v>
+      </c>
+      <c r="F12">
         <v>2</v>
       </c>
-      <c r="G12" s="3">
+      <c r="G12">
         <v>150</v>
       </c>
-      <c r="H12" s="3">
+      <c r="H12">
         <v>733</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A13" s="2"/>
-      <c r="B13" s="2">
+      <c r="A13" s="1"/>
+      <c r="B13" s="1">
         <v>1000205</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="C13" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="D13" s="3" t="s">
+      <c r="D13" t="s">
         <v>34</v>
       </c>
-      <c r="E13" s="3">
-        <v>900</v>
-      </c>
-      <c r="F13" s="3">
-        <v>1</v>
-      </c>
-      <c r="G13" s="3">
+      <c r="E13">
+        <v>900</v>
+      </c>
+      <c r="F13">
+        <v>1</v>
+      </c>
+      <c r="G13">
         <v>450</v>
       </c>
-      <c r="H13" s="3">
+      <c r="H13">
         <v>900</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A14" s="2"/>
-      <c r="B14" s="2">
+      <c r="A14" s="1"/>
+      <c r="B14" s="1">
         <v>1000301</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="C14" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D14" s="3" t="s">
+      <c r="D14" t="s">
         <v>35</v>
       </c>
-      <c r="E14" s="3">
-        <v>500</v>
-      </c>
-      <c r="F14" s="3">
+      <c r="E14">
+        <v>500</v>
+      </c>
+      <c r="F14">
         <v>0.85</v>
       </c>
-      <c r="G14" s="3">
+      <c r="G14">
         <v>319</v>
       </c>
-      <c r="H14" s="3">
+      <c r="H14">
         <v>319</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A15" s="2"/>
-      <c r="B15" s="2">
+      <c r="A15" s="1"/>
+      <c r="B15" s="1">
         <v>1000302</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="C15" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D15" s="3" t="s">
+      <c r="D15" t="s">
         <v>35</v>
       </c>
-      <c r="E15" s="3">
-        <v>900</v>
-      </c>
-      <c r="F15" s="3">
+      <c r="E15">
+        <v>900</v>
+      </c>
+      <c r="F15">
         <v>1.2</v>
       </c>
-      <c r="G15" s="3">
+      <c r="G15">
         <v>400</v>
       </c>
-      <c r="H15" s="3">
+      <c r="H15">
         <v>720</v>
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A16" s="2"/>
-      <c r="B16" s="2">
+      <c r="A16" s="1"/>
+      <c r="B16" s="1">
         <v>1000303</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="C16" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="D16" s="3" t="s">
+      <c r="D16" t="s">
         <v>35</v>
       </c>
-      <c r="E16" s="3">
-        <v>800</v>
-      </c>
-      <c r="F16" s="3">
-        <v>1</v>
-      </c>
-      <c r="G16" s="3">
+      <c r="E16">
+        <v>800</v>
+      </c>
+      <c r="F16">
+        <v>1</v>
+      </c>
+      <c r="G16">
         <v>500</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A17" s="2"/>
-      <c r="B17" s="2">
+      <c r="A17" s="1"/>
+      <c r="B17" s="1">
         <v>1000304</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="C17" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D17" s="3" t="s">
+      <c r="D17" t="s">
         <v>35</v>
       </c>
-      <c r="E17" s="3">
-        <v>900</v>
-      </c>
-      <c r="F17" s="3">
+      <c r="E17">
+        <v>900</v>
+      </c>
+      <c r="F17">
         <v>2</v>
       </c>
-      <c r="G17" s="3">
+      <c r="G17">
         <v>150</v>
       </c>
-      <c r="H17" s="3">
+      <c r="H17">
         <v>733</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A18" s="2"/>
-      <c r="B18" s="2">
+      <c r="A18" s="1"/>
+      <c r="B18" s="1">
         <v>1000305</v>
       </c>
-      <c r="C18" s="2" t="s">
+      <c r="C18" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="D18" s="3" t="s">
+      <c r="D18" t="s">
         <v>35</v>
       </c>
-      <c r="E18" s="3">
-        <v>900</v>
-      </c>
-      <c r="F18" s="3">
-        <v>1</v>
-      </c>
-      <c r="G18" s="3">
+      <c r="E18">
+        <v>900</v>
+      </c>
+      <c r="F18">
+        <v>1</v>
+      </c>
+      <c r="G18">
         <v>450</v>
       </c>
-      <c r="H18" s="3">
+      <c r="H18">
         <v>900</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A19" s="2"/>
-      <c r="B19" s="2">
+      <c r="A19" s="1"/>
+      <c r="B19" s="1">
         <v>1000401</v>
       </c>
-      <c r="C19" s="2" t="s">
+      <c r="C19" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D19" s="3" t="s">
+      <c r="D19" t="s">
         <v>36</v>
       </c>
-      <c r="E19" s="3">
-        <v>500</v>
-      </c>
-      <c r="F19" s="3">
+      <c r="E19">
+        <v>500</v>
+      </c>
+      <c r="F19">
         <v>0.85</v>
       </c>
-      <c r="G19" s="3">
+      <c r="G19">
         <v>319</v>
       </c>
-      <c r="H19" s="3">
+      <c r="H19">
         <v>319</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A20" s="2"/>
-      <c r="B20" s="2">
+      <c r="A20" s="1"/>
+      <c r="B20" s="1">
         <v>1000402</v>
       </c>
-      <c r="C20" s="2" t="s">
+      <c r="C20" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D20" s="3" t="s">
+      <c r="D20" t="s">
         <v>36</v>
       </c>
-      <c r="E20" s="3">
-        <v>900</v>
-      </c>
-      <c r="F20" s="3">
+      <c r="E20">
+        <v>900</v>
+      </c>
+      <c r="F20">
         <v>1.2</v>
       </c>
-      <c r="G20" s="3">
+      <c r="G20">
         <v>400</v>
       </c>
-      <c r="H20" s="3">
+      <c r="H20">
         <v>720</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A21" s="2"/>
-      <c r="B21" s="2">
+      <c r="A21" s="1"/>
+      <c r="B21" s="1">
         <v>1000403</v>
       </c>
-      <c r="C21" s="2" t="s">
+      <c r="C21" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="D21" s="3" t="s">
+      <c r="D21" t="s">
         <v>36</v>
       </c>
-      <c r="E21" s="3">
-        <v>800</v>
-      </c>
-      <c r="F21" s="3">
-        <v>1</v>
-      </c>
-      <c r="G21" s="3">
+      <c r="E21">
+        <v>800</v>
+      </c>
+      <c r="F21">
+        <v>1</v>
+      </c>
+      <c r="G21">
         <v>500</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A22" s="2"/>
-      <c r="B22" s="2">
+      <c r="A22" s="1"/>
+      <c r="B22" s="1">
         <v>1000404</v>
       </c>
-      <c r="C22" s="2" t="s">
+      <c r="C22" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D22" s="3" t="s">
+      <c r="D22" t="s">
         <v>36</v>
       </c>
-      <c r="E22" s="3">
-        <v>900</v>
-      </c>
-      <c r="F22" s="3">
+      <c r="E22">
+        <v>900</v>
+      </c>
+      <c r="F22">
         <v>2</v>
       </c>
-      <c r="G22" s="3">
+      <c r="G22">
         <v>150</v>
       </c>
-      <c r="H22" s="3">
+      <c r="H22">
         <v>733</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A23" s="2"/>
-      <c r="B23" s="2">
+      <c r="A23" s="1"/>
+      <c r="B23" s="1">
         <v>1000405</v>
       </c>
-      <c r="C23" s="2" t="s">
+      <c r="C23" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="D23" s="3" t="s">
+      <c r="D23" t="s">
         <v>36</v>
       </c>
-      <c r="E23" s="3">
-        <v>900</v>
-      </c>
-      <c r="F23" s="3">
-        <v>1</v>
-      </c>
-      <c r="G23" s="3">
+      <c r="E23">
+        <v>900</v>
+      </c>
+      <c r="F23">
+        <v>1</v>
+      </c>
+      <c r="G23">
         <v>450</v>
       </c>
-      <c r="H23" s="3">
+      <c r="H23">
         <v>900</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A24" s="2"/>
-      <c r="B24" s="2">
+      <c r="A24" s="1"/>
+      <c r="B24" s="1">
         <v>1000501</v>
       </c>
-      <c r="C24" s="2" t="s">
+      <c r="C24" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D24" s="3" t="s">
+      <c r="D24" t="s">
         <v>37</v>
       </c>
-      <c r="E24" s="3">
+      <c r="E24">
         <v>533</v>
       </c>
-      <c r="F24" s="3">
-        <v>1</v>
-      </c>
-      <c r="G24" s="3">
+      <c r="F24">
+        <v>1</v>
+      </c>
+      <c r="G24">
         <v>260</v>
       </c>
-      <c r="H24" s="3">
+      <c r="H24">
         <v>260</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A25" s="2"/>
-      <c r="B25" s="2">
+      <c r="A25" s="1"/>
+      <c r="B25" s="1">
         <v>1000502</v>
       </c>
-      <c r="C25" s="2" t="s">
+      <c r="C25" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D25" s="3" t="s">
+      <c r="D25" t="s">
         <v>37</v>
       </c>
-      <c r="E25" s="3">
-        <v>900</v>
-      </c>
-      <c r="F25" s="3">
-        <v>1</v>
-      </c>
-      <c r="G25" s="3">
+      <c r="E25">
+        <v>900</v>
+      </c>
+      <c r="F25">
+        <v>1</v>
+      </c>
+      <c r="G25">
         <v>270</v>
       </c>
-      <c r="H25" s="3">
+      <c r="H25">
         <v>650</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A26" s="2"/>
-      <c r="B26" s="2">
+      <c r="A26" s="1"/>
+      <c r="B26" s="1">
         <v>1000503</v>
       </c>
-      <c r="C26" s="2" t="s">
+      <c r="C26" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="D26" s="3" t="s">
+      <c r="D26" t="s">
         <v>37</v>
       </c>
-      <c r="E26" s="3">
-        <v>800</v>
-      </c>
-      <c r="F26" s="3">
-        <v>1</v>
-      </c>
-      <c r="G26" s="3">
+      <c r="E26">
+        <v>800</v>
+      </c>
+      <c r="F26">
+        <v>1</v>
+      </c>
+      <c r="G26">
         <v>500</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A27" s="2"/>
-      <c r="B27" s="2">
+      <c r="A27" s="1"/>
+      <c r="B27" s="1">
         <v>1000504</v>
       </c>
-      <c r="C27" s="2" t="s">
+      <c r="C27" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D27" s="3" t="s">
+      <c r="D27" t="s">
         <v>37</v>
       </c>
-      <c r="E27" s="3">
-        <v>900</v>
-      </c>
-      <c r="F27" s="3">
+      <c r="E27">
+        <v>900</v>
+      </c>
+      <c r="F27">
         <v>2</v>
       </c>
-      <c r="G27" s="3">
+      <c r="G27">
         <v>150</v>
       </c>
-      <c r="H27" s="3">
+      <c r="H27">
         <v>733</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A28" s="2"/>
-      <c r="B28" s="2">
+      <c r="A28" s="1"/>
+      <c r="B28" s="1">
         <v>1000505</v>
       </c>
-      <c r="C28" s="2" t="s">
+      <c r="C28" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="D28" s="3" t="s">
+      <c r="D28" t="s">
         <v>37</v>
       </c>
-      <c r="E28" s="3">
-        <v>900</v>
-      </c>
-      <c r="F28" s="3">
-        <v>1</v>
-      </c>
-      <c r="G28" s="3">
+      <c r="E28">
+        <v>900</v>
+      </c>
+      <c r="F28">
+        <v>1</v>
+      </c>
+      <c r="G28">
         <v>450</v>
       </c>
-      <c r="H28" s="3">
+      <c r="H28">
         <v>900</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A29" s="2"/>
-      <c r="B29" s="2">
+      <c r="A29" s="1"/>
+      <c r="B29" s="1">
         <v>1000601</v>
       </c>
-      <c r="C29" s="2" t="s">
+      <c r="C29" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D29" s="3" t="s">
+      <c r="D29" t="s">
         <v>38</v>
       </c>
-      <c r="E29" s="3">
-        <v>800</v>
-      </c>
-      <c r="F29" s="3">
+      <c r="E29">
+        <v>800</v>
+      </c>
+      <c r="F29">
         <v>1.5</v>
       </c>
-      <c r="G29" s="3">
+      <c r="G29">
         <v>650</v>
       </c>
-      <c r="H29" s="3">
+      <c r="H29">
         <v>650</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A30" s="2"/>
-      <c r="B30" s="2">
+      <c r="A30" s="1"/>
+      <c r="B30" s="1">
         <v>1000602</v>
       </c>
-      <c r="C30" s="2" t="s">
+      <c r="C30" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D30" s="3" t="s">
+      <c r="D30" t="s">
         <v>38</v>
       </c>
-      <c r="E30" s="3">
-        <v>900</v>
-      </c>
-      <c r="F30" s="3">
-        <v>1</v>
-      </c>
-      <c r="G30" s="3">
+      <c r="E30">
+        <v>900</v>
+      </c>
+      <c r="F30">
+        <v>1</v>
+      </c>
+      <c r="G30">
         <v>270</v>
       </c>
-      <c r="H30" s="3">
+      <c r="H30">
         <v>650</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A31" s="2"/>
-      <c r="B31" s="2">
+      <c r="A31" s="1"/>
+      <c r="B31" s="1">
         <v>1000603</v>
       </c>
-      <c r="C31" s="2" t="s">
+      <c r="C31" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="D31" s="3" t="s">
+      <c r="D31" t="s">
         <v>38</v>
       </c>
-      <c r="E31" s="3">
-        <v>800</v>
-      </c>
-      <c r="F31" s="3">
-        <v>1</v>
-      </c>
-      <c r="G31" s="3">
+      <c r="E31">
+        <v>800</v>
+      </c>
+      <c r="F31">
+        <v>1</v>
+      </c>
+      <c r="G31">
         <v>500</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A32" s="2"/>
-      <c r="B32" s="2">
+      <c r="A32" s="1"/>
+      <c r="B32" s="1">
         <v>1000604</v>
       </c>
-      <c r="C32" s="2" t="s">
+      <c r="C32" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D32" s="3" t="s">
+      <c r="D32" t="s">
         <v>38</v>
       </c>
-      <c r="E32" s="3">
-        <v>500</v>
-      </c>
-      <c r="F32" s="3">
-        <v>1</v>
-      </c>
-      <c r="G32" s="3">
+      <c r="E32">
+        <v>500</v>
+      </c>
+      <c r="F32">
+        <v>1</v>
+      </c>
+      <c r="G32">
         <v>100</v>
       </c>
-      <c r="H32" s="3">
+      <c r="H32">
         <v>325</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A33" s="2"/>
-      <c r="B33" s="2">
+      <c r="A33" s="1"/>
+      <c r="B33" s="1">
         <v>1000605</v>
       </c>
-      <c r="C33" s="2" t="s">
+      <c r="C33" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="D33" s="3" t="s">
+      <c r="D33" t="s">
         <v>38</v>
       </c>
-      <c r="E33" s="3">
+      <c r="E33">
         <v>833</v>
       </c>
-      <c r="F33" s="3">
-        <v>1</v>
-      </c>
-      <c r="G33" s="3">
+      <c r="F33">
+        <v>1</v>
+      </c>
+      <c r="G33">
         <v>520</v>
       </c>
-      <c r="H33" s="3">
+      <c r="H33">
         <v>800</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A34" s="2"/>
-      <c r="B34" s="2">
+      <c r="A34" s="1"/>
+      <c r="B34" s="1">
         <v>1000701</v>
       </c>
-      <c r="C34" s="2" t="s">
+      <c r="C34" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D34" s="4" t="s">
+      <c r="D34" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="E34" s="3">
-        <v>800</v>
-      </c>
-      <c r="F34" s="3">
+      <c r="E34">
+        <v>800</v>
+      </c>
+      <c r="F34">
         <v>1.5</v>
       </c>
-      <c r="G34" s="3">
+      <c r="G34">
         <v>650</v>
       </c>
-      <c r="H34" s="3">
+      <c r="H34">
         <v>650</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A35" s="2"/>
-      <c r="B35" s="2">
+      <c r="A35" s="1"/>
+      <c r="B35" s="1">
         <v>1000702</v>
       </c>
-      <c r="C35" s="2" t="s">
+      <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="3" t="s">
+      <c r="D35" t="s">
         <v>39</v>
       </c>
-      <c r="E35" s="3">
-        <v>900</v>
-      </c>
-      <c r="F35" s="3">
-        <v>1</v>
-      </c>
-      <c r="G35" s="3">
+      <c r="E35">
+        <v>900</v>
+      </c>
+      <c r="F35">
+        <v>1</v>
+      </c>
+      <c r="G35">
         <v>270</v>
       </c>
-      <c r="H35" s="3">
+      <c r="H35">
         <v>650</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A36" s="2"/>
-      <c r="B36" s="2">
+      <c r="A36" s="1"/>
+      <c r="B36" s="1">
         <v>1000703</v>
       </c>
-      <c r="C36" s="2" t="s">
+      <c r="C36" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="D36" s="3" t="s">
+      <c r="D36" t="s">
         <v>39</v>
       </c>
-      <c r="E36" s="3">
-        <v>800</v>
-      </c>
-      <c r="F36" s="3">
-        <v>1</v>
-      </c>
-      <c r="G36" s="3">
+      <c r="E36">
+        <v>800</v>
+      </c>
+      <c r="F36">
+        <v>1</v>
+      </c>
+      <c r="G36">
         <v>500</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A37" s="2"/>
-      <c r="B37" s="2">
+      <c r="A37" s="1"/>
+      <c r="B37" s="1">
         <v>1000704</v>
       </c>
-      <c r="C37" s="2" t="s">
+      <c r="C37" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D37" s="3" t="s">
+      <c r="D37" t="s">
         <v>39</v>
       </c>
-      <c r="E37" s="3">
-        <v>500</v>
-      </c>
-      <c r="F37" s="3">
-        <v>1</v>
-      </c>
-      <c r="G37" s="3">
+      <c r="E37">
+        <v>500</v>
+      </c>
+      <c r="F37">
+        <v>1</v>
+      </c>
+      <c r="G37">
         <v>100</v>
       </c>
-      <c r="H37" s="3">
+      <c r="H37">
         <v>325</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A38" s="2"/>
-      <c r="B38" s="2">
+      <c r="A38" s="1"/>
+      <c r="B38" s="1">
         <v>1000705</v>
       </c>
-      <c r="C38" s="2" t="s">
+      <c r="C38" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="D38" s="3" t="s">
+      <c r="D38" t="s">
         <v>39</v>
       </c>
-      <c r="E38" s="3">
+      <c r="E38">
         <v>833</v>
       </c>
-      <c r="F38" s="3">
-        <v>1</v>
-      </c>
-      <c r="G38" s="3">
+      <c r="F38">
+        <v>1</v>
+      </c>
+      <c r="G38">
         <v>520</v>
       </c>
-      <c r="H38" s="3">
+      <c r="H38">
         <v>800</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A39" s="2"/>
-      <c r="B39" s="2">
+      <c r="A39" s="1"/>
+      <c r="B39" s="1">
         <v>1000801</v>
       </c>
-      <c r="C39" s="2" t="s">
+      <c r="C39" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D39" s="3" t="s">
+      <c r="D39" t="s">
         <v>40</v>
       </c>
-      <c r="E39" s="3">
+      <c r="E39">
         <v>460</v>
       </c>
-      <c r="F39" s="3">
+      <c r="F39">
         <v>0.94</v>
       </c>
-      <c r="G39" s="3">
+      <c r="G39">
         <v>319</v>
       </c>
-      <c r="H39" s="3">
+      <c r="H39">
         <v>319</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A40" s="2"/>
-      <c r="B40" s="2">
+      <c r="A40" s="1"/>
+      <c r="B40" s="1">
         <v>1000802</v>
       </c>
-      <c r="C40" s="2" t="s">
+      <c r="C40" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D40" s="3" t="s">
+      <c r="D40" t="s">
         <v>40</v>
       </c>
-      <c r="E40" s="3">
+      <c r="E40">
         <v>1615</v>
       </c>
-      <c r="F40" s="3">
+      <c r="F40">
         <v>2</v>
       </c>
-      <c r="G40" s="3">
+      <c r="G40">
         <v>550</v>
       </c>
-      <c r="H40" s="3">
+      <c r="H40">
         <v>1300</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A41" s="2"/>
-      <c r="B41" s="2">
+      <c r="A41" s="1"/>
+      <c r="B41" s="1">
         <v>1000803</v>
       </c>
-      <c r="C41" s="2" t="s">
+      <c r="C41" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="D41" s="3" t="s">
+      <c r="D41" t="s">
         <v>40</v>
       </c>
-      <c r="E41" s="3">
-        <v>800</v>
-      </c>
-      <c r="F41" s="3">
-        <v>1</v>
-      </c>
-      <c r="G41" s="3">
+      <c r="E41">
+        <v>800</v>
+      </c>
+      <c r="F41">
+        <v>1</v>
+      </c>
+      <c r="G41">
         <v>500</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A42" s="2"/>
-      <c r="B42" s="2">
+      <c r="A42" s="1"/>
+      <c r="B42" s="1">
         <v>1000804</v>
       </c>
-      <c r="C42" s="2" t="s">
+      <c r="C42" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D42" s="3" t="s">
+      <c r="D42" t="s">
         <v>40</v>
       </c>
-      <c r="E42" s="3">
-        <v>900</v>
-      </c>
-      <c r="F42" s="3">
+      <c r="E42">
+        <v>900</v>
+      </c>
+      <c r="F42">
         <v>2</v>
       </c>
-      <c r="G42" s="3">
+      <c r="G42">
         <v>150</v>
       </c>
-      <c r="H42" s="3">
+      <c r="H42">
         <v>733</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A43" s="2"/>
-      <c r="B43" s="2">
+      <c r="A43" s="1"/>
+      <c r="B43" s="1">
         <v>1000805</v>
       </c>
-      <c r="C43" s="2" t="s">
+      <c r="C43" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="D43" s="3" t="s">
+      <c r="D43" t="s">
         <v>40</v>
       </c>
-      <c r="E43" s="3">
-        <v>900</v>
-      </c>
-      <c r="F43" s="3">
-        <v>1</v>
-      </c>
-      <c r="G43" s="3">
+      <c r="E43">
+        <v>900</v>
+      </c>
+      <c r="F43">
+        <v>1</v>
+      </c>
+      <c r="G43">
         <v>450</v>
       </c>
-      <c r="H43" s="3">
+      <c r="H43">
         <v>900</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A44" s="2"/>
-      <c r="B44" s="2">
+      <c r="A44" s="1"/>
+      <c r="B44" s="1">
         <v>1000901</v>
       </c>
-      <c r="C44" s="2" t="s">
+      <c r="C44" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D44" s="3" t="s">
+      <c r="D44" t="s">
         <v>41</v>
       </c>
-      <c r="E44" s="3">
-        <v>800</v>
-      </c>
-      <c r="F44" s="3">
+      <c r="E44">
+        <v>800</v>
+      </c>
+      <c r="F44">
         <v>1.5</v>
       </c>
-      <c r="G44" s="3">
+      <c r="G44">
         <v>650</v>
       </c>
-      <c r="H44" s="3">
+      <c r="H44">
         <v>650</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A45" s="2"/>
-      <c r="B45" s="2">
+      <c r="A45" s="1"/>
+      <c r="B45" s="1">
         <v>1000902</v>
       </c>
-      <c r="C45" s="2" t="s">
+      <c r="C45" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D45" s="3" t="s">
+      <c r="D45" t="s">
         <v>41</v>
       </c>
-      <c r="E45" s="3">
-        <v>900</v>
-      </c>
-      <c r="F45" s="3">
-        <v>1</v>
-      </c>
-      <c r="G45" s="3">
+      <c r="E45">
+        <v>900</v>
+      </c>
+      <c r="F45">
+        <v>1</v>
+      </c>
+      <c r="G45">
         <v>270</v>
       </c>
-      <c r="H45" s="3">
+      <c r="H45">
         <v>650</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A46" s="2"/>
-      <c r="B46" s="2">
+      <c r="A46" s="1"/>
+      <c r="B46" s="1">
         <v>1000903</v>
       </c>
-      <c r="C46" s="2" t="s">
+      <c r="C46" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="D46" s="3" t="s">
+      <c r="D46" t="s">
         <v>41</v>
       </c>
-      <c r="E46" s="3">
-        <v>800</v>
-      </c>
-      <c r="F46" s="3">
-        <v>1</v>
-      </c>
-      <c r="G46" s="3">
+      <c r="E46">
+        <v>800</v>
+      </c>
+      <c r="F46">
+        <v>1</v>
+      </c>
+      <c r="G46">
         <v>500</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A47" s="2"/>
-      <c r="B47" s="2">
+      <c r="A47" s="1"/>
+      <c r="B47" s="1">
         <v>1000904</v>
       </c>
-      <c r="C47" s="2" t="s">
+      <c r="C47" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D47" s="3" t="s">
+      <c r="D47" t="s">
         <v>41</v>
       </c>
-      <c r="E47" s="3">
-        <v>500</v>
-      </c>
-      <c r="F47" s="3">
-        <v>1</v>
-      </c>
-      <c r="G47" s="3">
+      <c r="E47">
+        <v>500</v>
+      </c>
+      <c r="F47">
+        <v>1</v>
+      </c>
+      <c r="G47">
         <v>100</v>
       </c>
-      <c r="H47" s="3">
+      <c r="H47">
         <v>325</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A48" s="2"/>
-      <c r="B48" s="2">
+      <c r="A48" s="1"/>
+      <c r="B48" s="1">
         <v>1000905</v>
       </c>
-      <c r="C48" s="2" t="s">
+      <c r="C48" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="D48" s="3" t="s">
+      <c r="D48" t="s">
         <v>41</v>
       </c>
-      <c r="E48" s="3">
+      <c r="E48">
         <v>833</v>
       </c>
-      <c r="F48" s="3">
-        <v>1</v>
-      </c>
-      <c r="G48" s="3">
+      <c r="F48">
+        <v>1</v>
+      </c>
+      <c r="G48">
         <v>520</v>
       </c>
-      <c r="H48" s="3">
+      <c r="H48">
         <v>800</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A49" s="2"/>
-      <c r="B49" s="2">
+      <c r="A49" s="1"/>
+      <c r="B49" s="1">
         <v>1001001</v>
       </c>
-      <c r="C49" s="2" t="s">
+      <c r="C49" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D49" s="4" t="s">
+      <c r="D49" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="E49" s="3">
-        <v>800</v>
-      </c>
-      <c r="F49" s="3">
+      <c r="E49">
+        <v>800</v>
+      </c>
+      <c r="F49">
         <v>1.5</v>
       </c>
-      <c r="G49" s="3">
+      <c r="G49">
         <v>650</v>
       </c>
-      <c r="H49" s="3">
+      <c r="H49">
         <v>650</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A50" s="2"/>
-      <c r="B50" s="2">
+      <c r="A50" s="1"/>
+      <c r="B50" s="1">
         <v>1001002</v>
       </c>
-      <c r="C50" s="2" t="s">
+      <c r="C50" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D50" s="4" t="s">
+      <c r="D50" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="E50" s="3">
-        <v>900</v>
-      </c>
-      <c r="F50" s="3">
-        <v>1</v>
-      </c>
-      <c r="G50" s="3">
+      <c r="E50">
+        <v>900</v>
+      </c>
+      <c r="F50">
+        <v>1</v>
+      </c>
+      <c r="G50">
         <v>270</v>
       </c>
-      <c r="H50" s="3">
+      <c r="H50">
         <v>650</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A51" s="2"/>
-      <c r="B51" s="2">
+      <c r="A51" s="1"/>
+      <c r="B51" s="1">
         <v>1001003</v>
       </c>
-      <c r="C51" s="2" t="s">
+      <c r="C51" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="D51" s="4" t="s">
+      <c r="D51" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="E51" s="3">
-        <v>800</v>
-      </c>
-      <c r="F51" s="3">
-        <v>1</v>
-      </c>
-      <c r="G51" s="3">
+      <c r="E51">
+        <v>800</v>
+      </c>
+      <c r="F51">
+        <v>1</v>
+      </c>
+      <c r="G51">
         <v>500</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B52" s="2">
+      <c r="B52" s="1">
         <v>1001004</v>
       </c>
-      <c r="C52" s="2" t="s">
+      <c r="C52" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D52" s="4" t="s">
+      <c r="D52" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="E52" s="3">
-        <v>500</v>
-      </c>
-      <c r="F52" s="3">
-        <v>1</v>
-      </c>
-      <c r="G52" s="3">
+      <c r="E52">
+        <v>500</v>
+      </c>
+      <c r="F52">
+        <v>1</v>
+      </c>
+      <c r="G52">
         <v>100</v>
       </c>
-      <c r="H52" s="3">
+      <c r="H52">
         <v>325</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B53" s="2">
+      <c r="B53" s="1">
         <v>1001005</v>
       </c>
-      <c r="C53" s="2" t="s">
+      <c r="C53" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="D53" s="4" t="s">
+      <c r="D53" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="E53" s="3">
+      <c r="E53">
         <v>833</v>
       </c>
-      <c r="F53" s="3">
-        <v>1</v>
-      </c>
-      <c r="G53" s="3">
+      <c r="F53">
+        <v>1</v>
+      </c>
+      <c r="G53">
         <v>520</v>
       </c>
-      <c r="H53" s="3">
+      <c r="H53">
         <v>800</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B54" s="2">
+      <c r="B54" s="1">
         <v>1001101</v>
       </c>
-      <c r="C54" s="2" t="s">
+      <c r="C54" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D54" s="3" t="s">
+      <c r="D54" t="s">
         <v>43</v>
       </c>
-      <c r="E54" s="3">
-        <v>500</v>
-      </c>
-      <c r="F54" s="3">
+      <c r="E54">
+        <v>500</v>
+      </c>
+      <c r="F54">
         <v>0.85</v>
       </c>
-      <c r="G54" s="3">
+      <c r="G54">
         <v>319</v>
       </c>
-      <c r="H54" s="3">
+      <c r="H54">
         <v>319</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B55" s="2">
+      <c r="B55" s="1">
         <v>1001102</v>
       </c>
-      <c r="C55" s="2" t="s">
+      <c r="C55" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D55" s="4" t="s">
+      <c r="D55" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="E55" s="3">
-        <v>900</v>
-      </c>
-      <c r="F55" s="3">
+      <c r="E55">
+        <v>900</v>
+      </c>
+      <c r="F55">
         <v>1.2</v>
       </c>
-      <c r="G55" s="3">
+      <c r="G55">
         <v>400</v>
       </c>
-      <c r="H55" s="3">
+      <c r="H55">
         <v>720</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B56" s="2">
+      <c r="B56" s="1">
         <v>1001103</v>
       </c>
-      <c r="C56" s="2" t="s">
+      <c r="C56" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="D56" s="3" t="s">
+      <c r="D56" t="s">
         <v>43</v>
       </c>
-      <c r="E56" s="3">
-        <v>800</v>
-      </c>
-      <c r="F56" s="3">
-        <v>1</v>
-      </c>
-      <c r="G56" s="3">
+      <c r="E56">
+        <v>800</v>
+      </c>
+      <c r="F56">
+        <v>1</v>
+      </c>
+      <c r="G56">
         <v>500</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B57" s="2">
+      <c r="B57" s="1">
         <v>1001104</v>
       </c>
-      <c r="C57" s="2" t="s">
+      <c r="C57" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D57" s="4" t="s">
+      <c r="D57" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="E57" s="3">
-        <v>900</v>
-      </c>
-      <c r="F57" s="3">
+      <c r="E57">
+        <v>900</v>
+      </c>
+      <c r="F57">
         <v>2</v>
       </c>
-      <c r="G57" s="3">
+      <c r="G57">
         <v>150</v>
       </c>
-      <c r="H57" s="3">
+      <c r="H57">
         <v>733</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B58" s="2">
+      <c r="B58" s="1">
         <v>1001105</v>
       </c>
-      <c r="C58" s="2" t="s">
+      <c r="C58" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="D58" s="3" t="s">
+      <c r="D58" t="s">
         <v>43</v>
       </c>
-      <c r="E58" s="3">
-        <v>900</v>
-      </c>
-      <c r="F58" s="3">
-        <v>1</v>
-      </c>
-      <c r="G58" s="3">
+      <c r="E58">
+        <v>900</v>
+      </c>
+      <c r="F58">
+        <v>1</v>
+      </c>
+      <c r="G58">
         <v>450</v>
       </c>
-      <c r="H58" s="3">
+      <c r="H58">
         <v>900</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B59" s="2">
+      <c r="B59" s="1">
         <v>1001201</v>
       </c>
-      <c r="C59" s="2" t="s">
+      <c r="C59" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D59" s="3" t="s">
+      <c r="D59" t="s">
         <v>44</v>
       </c>
-      <c r="E59" s="3">
-        <v>500</v>
-      </c>
-      <c r="F59" s="3">
+      <c r="E59">
+        <v>500</v>
+      </c>
+      <c r="F59">
         <v>0.85</v>
       </c>
-      <c r="G59" s="3">
+      <c r="G59">
         <v>319</v>
       </c>
-      <c r="H59" s="3">
+      <c r="H59">
         <v>319</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B60" s="2">
+      <c r="B60" s="1">
         <v>1001202</v>
       </c>
-      <c r="C60" s="2" t="s">
+      <c r="C60" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D60" s="3" t="s">
+      <c r="D60" t="s">
         <v>44</v>
       </c>
-      <c r="E60" s="3">
-        <v>900</v>
-      </c>
-      <c r="F60" s="3">
+      <c r="E60">
+        <v>900</v>
+      </c>
+      <c r="F60">
         <v>1.2</v>
       </c>
-      <c r="G60" s="3">
+      <c r="G60">
         <v>400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="H60">
         <v>720</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B61" s="2">
+      <c r="B61" s="1">
         <v>1001203</v>
       </c>
-      <c r="C61" s="2" t="s">
+      <c r="C61" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="D61" s="3" t="s">
+      <c r="D61" t="s">
         <v>44</v>
       </c>
-      <c r="E61" s="3">
-        <v>800</v>
-      </c>
-      <c r="F61" s="3">
-        <v>1</v>
-      </c>
-      <c r="G61" s="3">
+      <c r="E61">
+        <v>800</v>
+      </c>
+      <c r="F61">
+        <v>1</v>
+      </c>
+      <c r="G61">
         <v>500</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B62" s="2">
+      <c r="B62" s="1">
         <v>1001204</v>
       </c>
-      <c r="C62" s="2" t="s">
+      <c r="C62" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D62" s="3" t="s">
+      <c r="D62" t="s">
         <v>44</v>
       </c>
-      <c r="E62" s="3">
-        <v>900</v>
-      </c>
-      <c r="F62" s="3">
+      <c r="E62">
+        <v>900</v>
+      </c>
+      <c r="F62">
         <v>2</v>
       </c>
-      <c r="G62" s="3">
+      <c r="G62">
         <v>150</v>
       </c>
-      <c r="H62" s="3">
+      <c r="H62">
         <v>733</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B63" s="2">
+      <c r="B63" s="1">
         <v>1001205</v>
       </c>
-      <c r="C63" s="2" t="s">
+      <c r="C63" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="D63" s="3" t="s">
+      <c r="D63" t="s">
         <v>44</v>
       </c>
-      <c r="E63" s="3">
-        <v>900</v>
-      </c>
-      <c r="F63" s="3">
-        <v>1</v>
-      </c>
-      <c r="G63" s="3">
+      <c r="E63">
+        <v>900</v>
+      </c>
+      <c r="F63">
+        <v>1</v>
+      </c>
+      <c r="G63">
         <v>450</v>
       </c>
-      <c r="H63" s="3">
+      <c r="H63">
         <v>900</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B64" s="2">
+      <c r="B64" s="1">
         <v>1001301</v>
       </c>
-      <c r="C64" s="2" t="s">
+      <c r="C64" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D64" s="4" t="s">
+      <c r="D64" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="E64" s="3">
-        <v>800</v>
-      </c>
-      <c r="F64" s="3">
+      <c r="E64">
+        <v>800</v>
+      </c>
+      <c r="F64">
         <v>1.5</v>
       </c>
-      <c r="G64" s="3">
+      <c r="G64">
         <v>650</v>
       </c>
-      <c r="H64" s="3">
+      <c r="H64">
         <v>650</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B65" s="2">
+      <c r="B65" s="1">
         <v>1001302</v>
       </c>
-      <c r="C65" s="2" t="s">
+      <c r="C65" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D65" s="4" t="s">
+      <c r="D65" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="E65" s="3">
-        <v>900</v>
-      </c>
-      <c r="F65" s="3">
-        <v>1</v>
-      </c>
-      <c r="G65" s="3">
+      <c r="E65">
+        <v>900</v>
+      </c>
+      <c r="F65">
+        <v>1</v>
+      </c>
+      <c r="G65">
         <v>270</v>
       </c>
-      <c r="H65" s="3">
+      <c r="H65">
         <v>650</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B66" s="2">
+      <c r="B66" s="1">
         <v>1001303</v>
       </c>
-      <c r="C66" s="2" t="s">
+      <c r="C66" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="D66" s="4" t="s">
+      <c r="D66" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="E66" s="3">
-        <v>800</v>
-      </c>
-      <c r="F66" s="3">
-        <v>1</v>
-      </c>
-      <c r="G66" s="3">
+      <c r="E66">
+        <v>800</v>
+      </c>
+      <c r="F66">
+        <v>1</v>
+      </c>
+      <c r="G66">
         <v>500</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B67" s="2">
+      <c r="B67" s="1">
         <v>1001304</v>
       </c>
-      <c r="C67" s="2" t="s">
+      <c r="C67" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D67" s="4" t="s">
+      <c r="D67" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="E67" s="3">
-        <v>500</v>
-      </c>
-      <c r="F67" s="3">
-        <v>1</v>
-      </c>
-      <c r="G67" s="3">
+      <c r="E67">
+        <v>500</v>
+      </c>
+      <c r="F67">
+        <v>1</v>
+      </c>
+      <c r="G67">
         <v>100</v>
       </c>
-      <c r="H67" s="3">
+      <c r="H67">
         <v>325</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B68" s="2">
+      <c r="B68" s="1">
         <v>1001305</v>
       </c>
-      <c r="C68" s="2" t="s">
+      <c r="C68" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="D68" s="4" t="s">
+      <c r="D68" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="E68" s="3">
+      <c r="E68">
         <v>833</v>
       </c>
-      <c r="F68" s="3">
-        <v>1</v>
-      </c>
-      <c r="G68" s="3">
+      <c r="F68">
+        <v>1</v>
+      </c>
+      <c r="G68">
         <v>520</v>
       </c>
-      <c r="H68" s="3">
+      <c r="H68">
         <v>800</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A69" s="2"/>
-      <c r="B69" s="2">
+      <c r="A69" s="1"/>
+      <c r="B69" s="1">
         <v>1001401</v>
       </c>
-      <c r="C69" s="2" t="s">
+      <c r="C69" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D69" s="3" t="s">
+      <c r="D69" t="s">
         <v>55</v>
       </c>
-      <c r="E69" s="3">
+      <c r="E69">
         <v>460</v>
       </c>
-      <c r="F69" s="3">
+      <c r="F69">
         <v>0.94</v>
       </c>
-      <c r="G69" s="3">
+      <c r="G69">
         <v>319</v>
       </c>
-      <c r="H69" s="3">
+      <c r="H69">
         <v>319</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A70" s="2"/>
-      <c r="B70" s="2">
+      <c r="A70" s="1"/>
+      <c r="B70" s="1">
         <v>1001402</v>
       </c>
-      <c r="C70" s="2" t="s">
+      <c r="C70" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D70" s="3" t="s">
+      <c r="D70" t="s">
         <v>55</v>
       </c>
-      <c r="E70" s="3">
+      <c r="E70">
         <v>1615</v>
       </c>
-      <c r="F70" s="3">
+      <c r="F70">
         <v>2</v>
       </c>
-      <c r="G70" s="3">
+      <c r="G70">
         <v>550</v>
       </c>
-      <c r="H70" s="3">
+      <c r="H70">
         <v>1300</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A71" s="2"/>
-      <c r="B71" s="2">
+      <c r="A71" s="1"/>
+      <c r="B71" s="1">
         <v>1001403</v>
       </c>
-      <c r="C71" s="2" t="s">
+      <c r="C71" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="D71" s="3" t="s">
+      <c r="D71" t="s">
         <v>55</v>
       </c>
-      <c r="E71" s="3">
-        <v>800</v>
-      </c>
-      <c r="F71" s="3">
-        <v>1</v>
-      </c>
-      <c r="G71" s="3">
+      <c r="E71">
+        <v>800</v>
+      </c>
+      <c r="F71">
+        <v>1</v>
+      </c>
+      <c r="G71">
         <v>500</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A72" s="2"/>
-      <c r="B72" s="2">
+      <c r="A72" s="1"/>
+      <c r="B72" s="1">
         <v>1001404</v>
       </c>
-      <c r="C72" s="2" t="s">
+      <c r="C72" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D72" s="3" t="s">
+      <c r="D72" t="s">
         <v>55</v>
       </c>
-      <c r="E72" s="3">
-        <v>900</v>
-      </c>
-      <c r="F72" s="3">
+      <c r="E72">
+        <v>900</v>
+      </c>
+      <c r="F72">
         <v>2</v>
       </c>
-      <c r="G72" s="3">
+      <c r="G72">
         <v>150</v>
       </c>
-      <c r="H72" s="3">
+      <c r="H72">
         <v>733</v>
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A73" s="2"/>
-      <c r="B73" s="2">
+      <c r="A73" s="1"/>
+      <c r="B73" s="1">
         <v>1001405</v>
       </c>
-      <c r="C73" s="2" t="s">
+      <c r="C73" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="D73" s="3" t="s">
+      <c r="D73" t="s">
         <v>55</v>
       </c>
-      <c r="E73" s="3">
-        <v>900</v>
-      </c>
-      <c r="F73" s="3">
-        <v>1</v>
-      </c>
-      <c r="G73" s="3">
+      <c r="E73">
+        <v>900</v>
+      </c>
+      <c r="F73">
+        <v>1</v>
+      </c>
+      <c r="G73">
         <v>450</v>
       </c>
-      <c r="H73" s="3">
+      <c r="H73">
         <v>900</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A74" s="2"/>
-      <c r="B74" s="2">
+      <c r="A74" s="1"/>
+      <c r="B74" s="1">
         <v>1001501</v>
       </c>
-      <c r="C74" s="2" t="s">
+      <c r="C74" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D74" s="4" t="s">
+      <c r="D74" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="E74" s="3">
-        <v>500</v>
-      </c>
-      <c r="F74" s="3">
+      <c r="E74">
+        <v>500</v>
+      </c>
+      <c r="F74">
         <v>0.85</v>
       </c>
-      <c r="G74" s="3">
+      <c r="G74">
         <v>319</v>
       </c>
-      <c r="H74" s="3">
+      <c r="H74">
         <v>319</v>
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A75" s="2"/>
-      <c r="B75" s="2">
+      <c r="A75" s="1"/>
+      <c r="B75" s="1">
         <v>1001502</v>
       </c>
-      <c r="C75" s="2" t="s">
+      <c r="C75" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D75" s="4" t="s">
+      <c r="D75" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="E75" s="3">
-        <v>900</v>
-      </c>
-      <c r="F75" s="3">
+      <c r="E75">
+        <v>900</v>
+      </c>
+      <c r="F75">
         <v>1.2</v>
       </c>
-      <c r="G75" s="3">
+      <c r="G75">
         <v>400</v>
       </c>
-      <c r="H75" s="3">
+      <c r="H75">
         <v>720</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A76" s="2"/>
-      <c r="B76" s="2">
+      <c r="A76" s="1"/>
+      <c r="B76" s="1">
         <v>1001503</v>
       </c>
-      <c r="C76" s="2" t="s">
+      <c r="C76" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="D76" s="4" t="s">
+      <c r="D76" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="E76" s="3">
-        <v>800</v>
-      </c>
-      <c r="F76" s="3">
-        <v>1</v>
-      </c>
-      <c r="G76" s="3">
+      <c r="E76">
+        <v>800</v>
+      </c>
+      <c r="F76">
+        <v>1</v>
+      </c>
+      <c r="G76">
         <v>500</v>
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A77" s="2"/>
-      <c r="B77" s="2">
+      <c r="A77" s="1"/>
+      <c r="B77" s="1">
         <v>1001504</v>
       </c>
-      <c r="C77" s="2" t="s">
+      <c r="C77" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D77" s="4" t="s">
+      <c r="D77" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="E77" s="3">
-        <v>900</v>
-      </c>
-      <c r="F77" s="3">
+      <c r="E77">
+        <v>900</v>
+      </c>
+      <c r="F77">
         <v>2</v>
       </c>
-      <c r="G77" s="3">
+      <c r="G77">
         <v>150</v>
       </c>
-      <c r="H77" s="3">
+      <c r="H77">
         <v>733</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A78" s="2"/>
-      <c r="B78" s="2">
+      <c r="A78" s="1"/>
+      <c r="B78" s="1">
         <v>1001505</v>
       </c>
-      <c r="C78" s="2" t="s">
+      <c r="C78" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="D78" s="4" t="s">
+      <c r="D78" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="E78" s="3">
-        <v>900</v>
-      </c>
-      <c r="F78" s="3">
-        <v>1</v>
-      </c>
-      <c r="G78" s="3">
+      <c r="E78">
+        <v>900</v>
+      </c>
+      <c r="F78">
+        <v>1</v>
+      </c>
+      <c r="G78">
         <v>450</v>
       </c>
-      <c r="H78" s="3">
+      <c r="H78">
         <v>900</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B79" s="2">
+      <c r="B79" s="1">
         <v>1001601</v>
       </c>
-      <c r="C79" s="2" t="s">
+      <c r="C79" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D79" s="4" t="s">
+      <c r="D79" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="E79" s="3">
+      <c r="E79">
         <v>460</v>
       </c>
-      <c r="F79" s="3">
+      <c r="F79">
         <v>0.94</v>
       </c>
-      <c r="G79" s="3">
+      <c r="G79">
         <v>319</v>
       </c>
-      <c r="H79" s="3">
+      <c r="H79">
         <v>319</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B80" s="2">
+      <c r="B80" s="1">
         <v>1001602</v>
       </c>
-      <c r="C80" s="2" t="s">
+      <c r="C80" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D80" s="4" t="s">
+      <c r="D80" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="E80" s="3">
+      <c r="E80">
         <v>1615</v>
       </c>
-      <c r="F80" s="3">
+      <c r="F80">
         <v>2</v>
       </c>
-      <c r="G80" s="3">
+      <c r="G80">
         <v>550</v>
       </c>
-      <c r="H80" s="3">
+      <c r="H80">
         <v>1300</v>
       </c>
     </row>
     <row r="81" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B81" s="2">
+      <c r="B81" s="1">
         <v>1001603</v>
       </c>
-      <c r="C81" s="2" t="s">
+      <c r="C81" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="D81" s="4" t="s">
+      <c r="D81" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="E81" s="3">
-        <v>800</v>
-      </c>
-      <c r="F81" s="3">
-        <v>1</v>
-      </c>
-      <c r="G81" s="3">
+      <c r="E81">
+        <v>800</v>
+      </c>
+      <c r="F81">
+        <v>1</v>
+      </c>
+      <c r="G81">
         <v>500</v>
       </c>
     </row>
     <row r="82" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B82" s="2">
+      <c r="B82" s="1">
         <v>1001604</v>
       </c>
-      <c r="C82" s="2" t="s">
+      <c r="C82" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D82" s="4" t="s">
+      <c r="D82" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="E82" s="3">
-        <v>900</v>
-      </c>
-      <c r="F82" s="3">
+      <c r="E82">
+        <v>900</v>
+      </c>
+      <c r="F82">
         <v>2</v>
       </c>
-      <c r="G82" s="3">
+      <c r="G82">
         <v>150</v>
       </c>
-      <c r="H82" s="3">
+      <c r="H82">
         <v>733</v>
       </c>
     </row>
     <row r="83" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B83" s="2">
+      <c r="B83" s="1">
         <v>1001605</v>
       </c>
-      <c r="C83" s="2" t="s">
+      <c r="C83" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="D83" s="4" t="s">
+      <c r="D83" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="E83" s="3">
-        <v>900</v>
-      </c>
-      <c r="F83" s="3">
-        <v>1</v>
-      </c>
-      <c r="G83" s="3">
+      <c r="E83">
+        <v>900</v>
+      </c>
+      <c r="F83">
+        <v>1</v>
+      </c>
+      <c r="G83">
         <v>450</v>
       </c>
-      <c r="H83" s="3">
+      <c r="H83">
         <v>900</v>
       </c>
     </row>
     <row r="84" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B84" s="2">
+      <c r="B84" s="1">
         <v>1001701</v>
       </c>
-      <c r="C84" s="2" t="s">
+      <c r="C84" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D84" s="4" t="s">
+      <c r="D84" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="E84" s="3">
+      <c r="E84">
         <v>460</v>
       </c>
-      <c r="F84" s="3">
+      <c r="F84">
         <v>0.94</v>
       </c>
-      <c r="G84" s="3">
+      <c r="G84">
         <v>319</v>
       </c>
-      <c r="H84" s="3">
+      <c r="H84">
         <v>319</v>
       </c>
     </row>
     <row r="85" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B85" s="2">
+      <c r="B85" s="1">
         <v>1001702</v>
       </c>
-      <c r="C85" s="2" t="s">
+      <c r="C85" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D85" s="4" t="s">
+      <c r="D85" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="E85" s="3">
+      <c r="E85">
         <v>1615</v>
       </c>
-      <c r="F85" s="3">
+      <c r="F85">
         <v>2</v>
       </c>
-      <c r="G85" s="3">
+      <c r="G85">
         <v>550</v>
       </c>
-      <c r="H85" s="3">
+      <c r="H85">
         <v>1300</v>
       </c>
     </row>
     <row r="86" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B86" s="2">
+      <c r="B86" s="1">
         <v>1001703</v>
       </c>
-      <c r="C86" s="2" t="s">
+      <c r="C86" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="D86" s="4" t="s">
+      <c r="D86" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="E86" s="3">
-        <v>800</v>
-      </c>
-      <c r="F86" s="3">
-        <v>1</v>
-      </c>
-      <c r="G86" s="3">
+      <c r="E86">
+        <v>800</v>
+      </c>
+      <c r="F86">
+        <v>1</v>
+      </c>
+      <c r="G86">
         <v>500</v>
       </c>
     </row>
     <row r="87" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B87" s="2">
+      <c r="B87" s="1">
         <v>1001704</v>
       </c>
-      <c r="C87" s="2" t="s">
+      <c r="C87" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D87" s="4" t="s">
+      <c r="D87" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="E87" s="3">
-        <v>900</v>
-      </c>
-      <c r="F87" s="3">
+      <c r="E87">
+        <v>900</v>
+      </c>
+      <c r="F87">
         <v>2</v>
       </c>
-      <c r="G87" s="3">
+      <c r="G87">
         <v>150</v>
       </c>
-      <c r="H87" s="3">
+      <c r="H87">
         <v>733</v>
       </c>
     </row>
     <row r="88" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B88" s="2">
+      <c r="B88" s="1">
         <v>1001705</v>
       </c>
-      <c r="C88" s="2" t="s">
+      <c r="C88" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="D88" s="4" t="s">
+      <c r="D88" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="E88" s="3">
-        <v>900</v>
-      </c>
-      <c r="F88" s="3">
-        <v>1</v>
-      </c>
-      <c r="G88" s="3">
+      <c r="E88">
+        <v>900</v>
+      </c>
+      <c r="F88">
+        <v>1</v>
+      </c>
+      <c r="G88">
         <v>450</v>
       </c>
-      <c r="H88" s="3">
+      <c r="H88">
         <v>900</v>
       </c>
     </row>
     <row r="89" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B89" s="2">
+      <c r="B89" s="1">
         <v>1001801</v>
       </c>
-      <c r="C89" s="2" t="s">
+      <c r="C89" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D89" s="4" t="s">
+      <c r="D89" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="E89" s="3">
+      <c r="E89">
         <v>460</v>
       </c>
-      <c r="F89" s="3">
+      <c r="F89">
         <v>0.94</v>
       </c>
-      <c r="G89" s="3">
+      <c r="G89">
         <v>319</v>
       </c>
-      <c r="H89" s="3">
+      <c r="H89">
         <v>319</v>
       </c>
     </row>
     <row r="90" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B90" s="2">
+      <c r="B90" s="1">
         <v>1001802</v>
       </c>
-      <c r="C90" s="2" t="s">
+      <c r="C90" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D90" s="4" t="s">
+      <c r="D90" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="E90" s="3">
+      <c r="E90">
         <v>1615</v>
       </c>
-      <c r="F90" s="3">
+      <c r="F90">
         <v>2</v>
       </c>
-      <c r="G90" s="3">
+      <c r="G90">
         <v>550</v>
       </c>
-      <c r="H90" s="3">
+      <c r="H90">
         <v>1300</v>
       </c>
     </row>
     <row r="91" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B91" s="2">
+      <c r="B91" s="1">
         <v>1001803</v>
       </c>
-      <c r="C91" s="2" t="s">
+      <c r="C91" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="D91" s="4" t="s">
+      <c r="D91" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="E91" s="3">
-        <v>800</v>
-      </c>
-      <c r="F91" s="3">
-        <v>1</v>
-      </c>
-      <c r="G91" s="3">
+      <c r="E91">
+        <v>800</v>
+      </c>
+      <c r="F91">
+        <v>1</v>
+      </c>
+      <c r="G91">
         <v>500</v>
       </c>
     </row>
     <row r="92" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B92" s="2">
+      <c r="B92" s="1">
         <v>1001804</v>
       </c>
-      <c r="C92" s="2" t="s">
+      <c r="C92" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D92" s="4" t="s">
+      <c r="D92" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="E92" s="3">
-        <v>900</v>
-      </c>
-      <c r="F92" s="3">
+      <c r="E92">
+        <v>900</v>
+      </c>
+      <c r="F92">
         <v>2</v>
       </c>
-      <c r="G92" s="3">
+      <c r="G92">
         <v>150</v>
       </c>
-      <c r="H92" s="3">
+      <c r="H92">
         <v>733</v>
       </c>
     </row>
     <row r="93" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B93" s="2">
+      <c r="B93" s="1">
         <v>1001805</v>
       </c>
-      <c r="C93" s="2" t="s">
+      <c r="C93" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="D93" s="4" t="s">
+      <c r="D93" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="E93" s="3">
-        <v>900</v>
-      </c>
-      <c r="F93" s="3">
-        <v>1</v>
-      </c>
-      <c r="G93" s="3">
+      <c r="E93">
+        <v>900</v>
+      </c>
+      <c r="F93">
+        <v>1</v>
+      </c>
+      <c r="G93">
         <v>450</v>
       </c>
-      <c r="H93" s="3">
+      <c r="H93">
         <v>900</v>
       </c>
     </row>
     <row r="94" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B94" s="2">
+      <c r="B94" s="1">
         <v>1001901</v>
       </c>
-      <c r="C94" s="2" t="s">
+      <c r="C94" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D94" s="4" t="s">
+      <c r="D94" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="E94" s="3">
-        <v>800</v>
-      </c>
-      <c r="F94" s="3">
+      <c r="E94">
+        <v>800</v>
+      </c>
+      <c r="F94">
         <v>1.5</v>
       </c>
-      <c r="G94" s="3">
+      <c r="G94">
         <v>650</v>
       </c>
-      <c r="H94" s="3">
+      <c r="H94">
         <v>650</v>
       </c>
     </row>
     <row r="95" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B95" s="2">
+      <c r="B95" s="1">
         <v>1001902</v>
       </c>
-      <c r="C95" s="2" t="s">
+      <c r="C95" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D95" s="4" t="s">
+      <c r="D95" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="E95" s="3">
-        <v>900</v>
-      </c>
-      <c r="F95" s="3">
-        <v>1</v>
-      </c>
-      <c r="G95" s="3">
+      <c r="E95">
+        <v>900</v>
+      </c>
+      <c r="F95">
+        <v>1</v>
+      </c>
+      <c r="G95">
         <v>270</v>
       </c>
-      <c r="H95" s="3">
+      <c r="H95">
         <v>650</v>
       </c>
     </row>
     <row r="96" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B96" s="2">
+      <c r="B96" s="1">
         <v>1001903</v>
       </c>
-      <c r="C96" s="2" t="s">
+      <c r="C96" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="D96" s="4" t="s">
+      <c r="D96" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="E96" s="3">
-        <v>800</v>
-      </c>
-      <c r="F96" s="3">
-        <v>1</v>
-      </c>
-      <c r="G96" s="3">
+      <c r="E96">
+        <v>800</v>
+      </c>
+      <c r="F96">
+        <v>1</v>
+      </c>
+      <c r="G96">
         <v>500</v>
       </c>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B97" s="2">
+      <c r="B97" s="1">
         <v>1001904</v>
       </c>
-      <c r="C97" s="2" t="s">
+      <c r="C97" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D97" s="4" t="s">
+      <c r="D97" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="E97" s="3">
-        <v>500</v>
-      </c>
-      <c r="F97" s="3">
-        <v>1</v>
-      </c>
-      <c r="G97" s="3">
+      <c r="E97">
+        <v>500</v>
+      </c>
+      <c r="F97">
+        <v>1</v>
+      </c>
+      <c r="G97">
         <v>100</v>
       </c>
-      <c r="H97" s="3">
+      <c r="H97">
         <v>325</v>
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B98" s="2">
+      <c r="B98" s="1">
         <v>1001905</v>
       </c>
-      <c r="C98" s="2" t="s">
+      <c r="C98" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="D98" s="4" t="s">
+      <c r="D98" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="E98" s="3">
+      <c r="E98">
         <v>833</v>
       </c>
-      <c r="F98" s="3">
-        <v>1</v>
-      </c>
-      <c r="G98" s="3">
+      <c r="F98">
+        <v>1</v>
+      </c>
+      <c r="G98">
         <v>520</v>
       </c>
-      <c r="H98" s="3">
+      <c r="H98">
         <v>800</v>
       </c>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A99" s="2"/>
-      <c r="B99" s="2">
+      <c r="A99" s="1"/>
+      <c r="B99" s="1">
         <v>1002001</v>
       </c>
-      <c r="C99" s="2" t="s">
+      <c r="C99" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D99" s="4" t="s">
+      <c r="D99" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="E99" s="3">
-        <v>800</v>
-      </c>
-      <c r="F99" s="3">
+      <c r="E99">
+        <v>800</v>
+      </c>
+      <c r="F99">
         <v>1.5</v>
       </c>
-      <c r="G99" s="3">
+      <c r="G99">
         <v>650</v>
       </c>
-      <c r="H99" s="3">
+      <c r="H99">
         <v>650</v>
       </c>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A100" s="2"/>
-      <c r="B100" s="2">
+      <c r="A100" s="1"/>
+      <c r="B100" s="1">
         <v>1002002</v>
       </c>
-      <c r="C100" s="2" t="s">
+      <c r="C100" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D100" s="4" t="s">
+      <c r="D100" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="E100" s="3">
-        <v>900</v>
-      </c>
-      <c r="F100" s="3">
-        <v>1</v>
-      </c>
-      <c r="G100" s="3">
+      <c r="E100">
+        <v>900</v>
+      </c>
+      <c r="F100">
+        <v>1</v>
+      </c>
+      <c r="G100">
         <v>270</v>
       </c>
-      <c r="H100" s="3">
+      <c r="H100">
         <v>650</v>
       </c>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A101" s="2"/>
-      <c r="B101" s="2">
+      <c r="A101" s="1"/>
+      <c r="B101" s="1">
         <v>1002003</v>
       </c>
-      <c r="C101" s="2" t="s">
+      <c r="C101" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="D101" s="4" t="s">
+      <c r="D101" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="E101" s="3">
-        <v>800</v>
-      </c>
-      <c r="F101" s="3">
-        <v>1</v>
-      </c>
-      <c r="G101" s="3">
+      <c r="E101">
+        <v>800</v>
+      </c>
+      <c r="F101">
+        <v>1</v>
+      </c>
+      <c r="G101">
         <v>500</v>
       </c>
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A102" s="2"/>
-      <c r="B102" s="2">
+      <c r="A102" s="1"/>
+      <c r="B102" s="1">
         <v>1002004</v>
       </c>
-      <c r="C102" s="2" t="s">
+      <c r="C102" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D102" s="4" t="s">
+      <c r="D102" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="E102" s="3">
-        <v>500</v>
-      </c>
-      <c r="F102" s="3">
-        <v>1</v>
-      </c>
-      <c r="G102" s="3">
+      <c r="E102">
+        <v>500</v>
+      </c>
+      <c r="F102">
+        <v>1</v>
+      </c>
+      <c r="G102">
         <v>100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="H102">
         <v>325</v>
       </c>
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A103" s="2"/>
-      <c r="B103" s="2">
+      <c r="A103" s="1"/>
+      <c r="B103" s="1">
         <v>1002005</v>
       </c>
-      <c r="C103" s="2" t="s">
+      <c r="C103" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="D103" s="4" t="s">
+      <c r="D103" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="E103" s="3">
+      <c r="E103">
         <v>833</v>
       </c>
-      <c r="F103" s="3">
-        <v>1</v>
-      </c>
-      <c r="G103" s="3">
+      <c r="F103">
+        <v>1</v>
+      </c>
+      <c r="G103">
         <v>520</v>
       </c>
-      <c r="H103" s="3">
+      <c r="H103">
         <v>800</v>
       </c>
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A104" s="2"/>
-      <c r="B104" s="2">
+      <c r="A104" s="1"/>
+      <c r="B104" s="1">
         <v>1002101</v>
       </c>
-      <c r="C104" s="2" t="s">
+      <c r="C104" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D104" s="4" t="s">
+      <c r="D104" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="E104" s="3">
-        <v>800</v>
-      </c>
-      <c r="F104" s="3">
+      <c r="E104">
+        <v>800</v>
+      </c>
+      <c r="F104">
         <v>1.5</v>
       </c>
-      <c r="G104" s="3">
+      <c r="G104">
         <v>650</v>
       </c>
-      <c r="H104" s="3">
+      <c r="H104">
         <v>650</v>
       </c>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A105" s="2"/>
-      <c r="B105" s="2">
+      <c r="A105" s="1"/>
+      <c r="B105" s="1">
         <v>1002102</v>
       </c>
-      <c r="C105" s="2" t="s">
+      <c r="C105" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D105" s="4" t="s">
+      <c r="D105" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="E105" s="3">
-        <v>900</v>
-      </c>
-      <c r="F105" s="3">
-        <v>1</v>
-      </c>
-      <c r="G105" s="3">
+      <c r="E105">
+        <v>900</v>
+      </c>
+      <c r="F105">
+        <v>1</v>
+      </c>
+      <c r="G105">
         <v>270</v>
       </c>
-      <c r="H105" s="3">
+      <c r="H105">
         <v>650</v>
       </c>
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A106" s="2"/>
-      <c r="B106" s="2">
+      <c r="A106" s="1"/>
+      <c r="B106" s="1">
         <v>1002103</v>
       </c>
-      <c r="C106" s="2" t="s">
+      <c r="C106" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="D106" s="4" t="s">
+      <c r="D106" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="E106" s="3">
-        <v>800</v>
-      </c>
-      <c r="F106" s="3">
-        <v>1</v>
-      </c>
-      <c r="G106" s="3">
+      <c r="E106">
+        <v>800</v>
+      </c>
+      <c r="F106">
+        <v>1</v>
+      </c>
+      <c r="G106">
         <v>500</v>
       </c>
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A107" s="2"/>
-      <c r="B107" s="2">
+      <c r="A107" s="1"/>
+      <c r="B107" s="1">
         <v>1002104</v>
       </c>
-      <c r="C107" s="2" t="s">
+      <c r="C107" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D107" s="4" t="s">
+      <c r="D107" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="E107" s="3">
-        <v>500</v>
-      </c>
-      <c r="F107" s="3">
-        <v>1</v>
-      </c>
-      <c r="G107" s="3">
+      <c r="E107">
+        <v>500</v>
+      </c>
+      <c r="F107">
+        <v>1</v>
+      </c>
+      <c r="G107">
         <v>100</v>
       </c>
-      <c r="H107" s="3">
+      <c r="H107">
         <v>325</v>
       </c>
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A108" s="2"/>
-      <c r="B108" s="2">
+      <c r="A108" s="1"/>
+      <c r="B108" s="1">
         <v>1002105</v>
       </c>
-      <c r="C108" s="2" t="s">
+      <c r="C108" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="D108" s="4" t="s">
+      <c r="D108" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="E108" s="3">
+      <c r="E108">
         <v>833</v>
       </c>
-      <c r="F108" s="3">
-        <v>1</v>
-      </c>
-      <c r="G108" s="3">
+      <c r="F108">
+        <v>1</v>
+      </c>
+      <c r="G108">
         <v>520</v>
       </c>
-      <c r="H108" s="3">
+      <c r="H108">
         <v>800</v>
       </c>
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A109" s="2"/>
-      <c r="B109" s="2">
+      <c r="A109" s="1"/>
+      <c r="B109" s="1">
         <v>1002201</v>
       </c>
-      <c r="C109" s="2" t="s">
+      <c r="C109" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D109" s="4" t="s">
+      <c r="D109" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="E109" s="3">
-        <v>800</v>
-      </c>
-      <c r="F109" s="3">
+      <c r="E109">
+        <v>800</v>
+      </c>
+      <c r="F109">
         <v>1.5</v>
       </c>
-      <c r="G109" s="3">
+      <c r="G109">
         <v>650</v>
       </c>
-      <c r="H109" s="3">
+      <c r="H109">
         <v>650</v>
       </c>
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A110" s="2"/>
-      <c r="B110" s="2">
+      <c r="A110" s="1"/>
+      <c r="B110" s="1">
         <v>1002202</v>
       </c>
-      <c r="C110" s="2" t="s">
+      <c r="C110" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D110" s="4" t="s">
+      <c r="D110" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="E110" s="3">
-        <v>900</v>
-      </c>
-      <c r="F110" s="3">
-        <v>1</v>
-      </c>
-      <c r="G110" s="3">
+      <c r="E110">
+        <v>900</v>
+      </c>
+      <c r="F110">
+        <v>1</v>
+      </c>
+      <c r="G110">
         <v>270</v>
       </c>
-      <c r="H110" s="3">
+      <c r="H110">
         <v>650</v>
       </c>
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A111" s="2"/>
-      <c r="B111" s="2">
+      <c r="A111" s="1"/>
+      <c r="B111" s="1">
         <v>1002203</v>
       </c>
-      <c r="C111" s="2" t="s">
+      <c r="C111" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="D111" s="4" t="s">
+      <c r="D111" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="E111" s="3">
-        <v>800</v>
-      </c>
-      <c r="F111" s="3">
-        <v>1</v>
-      </c>
-      <c r="G111" s="3">
+      <c r="E111">
+        <v>800</v>
+      </c>
+      <c r="F111">
+        <v>1</v>
+      </c>
+      <c r="G111">
         <v>500</v>
       </c>
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A112" s="2"/>
-      <c r="B112" s="2">
+      <c r="A112" s="1"/>
+      <c r="B112" s="1">
         <v>1002204</v>
       </c>
-      <c r="C112" s="2" t="s">
+      <c r="C112" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D112" s="4" t="s">
+      <c r="D112" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="E112" s="3">
-        <v>500</v>
-      </c>
-      <c r="F112" s="3">
-        <v>1</v>
-      </c>
-      <c r="G112" s="3">
+      <c r="E112">
+        <v>500</v>
+      </c>
+      <c r="F112">
+        <v>1</v>
+      </c>
+      <c r="G112">
         <v>100</v>
       </c>
-      <c r="H112" s="3">
+      <c r="H112">
         <v>325</v>
       </c>
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A113" s="2"/>
-      <c r="B113" s="2">
+      <c r="A113" s="1"/>
+      <c r="B113" s="1">
         <v>1002205</v>
       </c>
-      <c r="C113" s="2" t="s">
+      <c r="C113" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="D113" s="4" t="s">
+      <c r="D113" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="E113" s="3">
+      <c r="E113">
         <v>833</v>
       </c>
-      <c r="F113" s="3">
-        <v>1</v>
-      </c>
-      <c r="G113" s="3">
+      <c r="F113">
+        <v>1</v>
+      </c>
+      <c r="G113">
         <v>520</v>
       </c>
-      <c r="H113" s="3">
+      <c r="H113">
         <v>800</v>
       </c>
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A114" s="2"/>
-      <c r="B114" s="2">
+      <c r="A114" s="1"/>
+      <c r="B114" s="1">
         <v>1002301</v>
       </c>
-      <c r="C114" s="2" t="s">
+      <c r="C114" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D114" s="4" t="s">
+      <c r="D114" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="E114" s="3">
-        <v>800</v>
-      </c>
-      <c r="F114" s="3">
+      <c r="E114">
+        <v>800</v>
+      </c>
+      <c r="F114">
         <v>1.5</v>
       </c>
-      <c r="G114" s="3">
+      <c r="G114">
         <v>650</v>
       </c>
-      <c r="H114" s="3">
+      <c r="H114">
         <v>650</v>
       </c>
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A115" s="2"/>
-      <c r="B115" s="2">
+      <c r="A115" s="1"/>
+      <c r="B115" s="1">
         <v>1002302</v>
       </c>
-      <c r="C115" s="2" t="s">
+      <c r="C115" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D115" s="4" t="s">
+      <c r="D115" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="E115" s="3">
-        <v>900</v>
-      </c>
-      <c r="F115" s="3">
-        <v>1</v>
-      </c>
-      <c r="G115" s="3">
+      <c r="E115">
+        <v>900</v>
+      </c>
+      <c r="F115">
+        <v>1</v>
+      </c>
+      <c r="G115">
         <v>270</v>
       </c>
-      <c r="H115" s="3">
+      <c r="H115">
         <v>650</v>
       </c>
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A116" s="2"/>
-      <c r="B116" s="2">
+      <c r="A116" s="1"/>
+      <c r="B116" s="1">
         <v>1002303</v>
       </c>
-      <c r="C116" s="2" t="s">
+      <c r="C116" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="D116" s="4" t="s">
+      <c r="D116" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="E116" s="3">
-        <v>800</v>
-      </c>
-      <c r="F116" s="3">
-        <v>1</v>
-      </c>
-      <c r="G116" s="3">
+      <c r="E116">
+        <v>800</v>
+      </c>
+      <c r="F116">
+        <v>1</v>
+      </c>
+      <c r="G116">
         <v>500</v>
       </c>
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A117" s="2"/>
-      <c r="B117" s="2">
+      <c r="A117" s="1"/>
+      <c r="B117" s="1">
         <v>1002304</v>
       </c>
-      <c r="C117" s="2" t="s">
+      <c r="C117" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D117" s="4" t="s">
+      <c r="D117" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="E117" s="3">
-        <v>500</v>
-      </c>
-      <c r="F117" s="3">
-        <v>1</v>
-      </c>
-      <c r="G117" s="3">
+      <c r="E117">
+        <v>500</v>
+      </c>
+      <c r="F117">
+        <v>1</v>
+      </c>
+      <c r="G117">
         <v>100</v>
       </c>
-      <c r="H117" s="3">
+      <c r="H117">
         <v>325</v>
       </c>
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A118" s="2"/>
-      <c r="B118" s="2">
+      <c r="A118" s="1"/>
+      <c r="B118" s="1">
         <v>1002305</v>
       </c>
-      <c r="C118" s="2" t="s">
+      <c r="C118" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="D118" s="4" t="s">
+      <c r="D118" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="E118" s="3">
+      <c r="E118">
         <v>833</v>
       </c>
-      <c r="F118" s="3">
-        <v>1</v>
-      </c>
-      <c r="G118" s="3">
+      <c r="F118">
+        <v>1</v>
+      </c>
+      <c r="G118">
         <v>520</v>
       </c>
-      <c r="H118" s="3">
-        <v>800</v>
+      <c r="H118">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="119" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B119" s="1">
+        <v>1002401</v>
+      </c>
+      <c r="C119" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D119" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="E119">
+        <v>800</v>
+      </c>
+      <c r="F119">
+        <v>1.5</v>
+      </c>
+      <c r="G119">
+        <v>650</v>
+      </c>
+      <c r="H119">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="120" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B120" s="1">
+        <v>1002402</v>
+      </c>
+      <c r="C120" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D120" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="E120">
+        <v>900</v>
+      </c>
+      <c r="F120">
+        <v>1</v>
+      </c>
+      <c r="G120">
+        <v>270</v>
+      </c>
+      <c r="H120">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="121" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B121" s="1">
+        <v>1002403</v>
+      </c>
+      <c r="C121" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D121" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="E121">
+        <v>800</v>
+      </c>
+      <c r="F121">
+        <v>1</v>
+      </c>
+      <c r="G121">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="122" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B122" s="1">
+        <v>1002404</v>
+      </c>
+      <c r="C122" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D122" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="E122">
+        <v>500</v>
+      </c>
+      <c r="F122">
+        <v>1</v>
+      </c>
+      <c r="G122">
+        <v>100</v>
+      </c>
+      <c r="H122">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="123" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B123" s="1">
+        <v>1002405</v>
+      </c>
+      <c r="C123" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D123" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="E123">
+        <v>833</v>
+      </c>
+      <c r="F123">
+        <v>1</v>
+      </c>
+      <c r="G123">
+        <v>520</v>
+      </c>
+      <c r="H123">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="124" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B124" s="1">
+        <v>1002501</v>
+      </c>
+      <c r="C124" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D124" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="E124">
+        <v>460</v>
+      </c>
+      <c r="F124">
+        <v>0.94</v>
+      </c>
+      <c r="G124">
+        <v>319</v>
+      </c>
+      <c r="H124">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="125" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B125" s="1">
+        <v>1002502</v>
+      </c>
+      <c r="C125" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D125" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="E125">
+        <v>1615</v>
+      </c>
+      <c r="F125">
+        <v>2</v>
+      </c>
+      <c r="G125">
+        <v>550</v>
+      </c>
+      <c r="H125">
+        <v>1300</v>
+      </c>
+    </row>
+    <row r="126" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B126" s="1">
+        <v>1002503</v>
+      </c>
+      <c r="C126" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D126" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="E126">
+        <v>800</v>
+      </c>
+      <c r="F126">
+        <v>1</v>
+      </c>
+      <c r="G126">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="127" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B127" s="1">
+        <v>1002504</v>
+      </c>
+      <c r="C127" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D127" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="E127">
+        <v>900</v>
+      </c>
+      <c r="F127">
+        <v>2</v>
+      </c>
+      <c r="G127">
+        <v>150</v>
+      </c>
+      <c r="H127">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="128" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B128" s="1">
+        <v>1002505</v>
+      </c>
+      <c r="C128" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D128" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="E128">
+        <v>900</v>
+      </c>
+      <c r="F128">
+        <v>1</v>
+      </c>
+      <c r="G128">
+        <v>450</v>
+      </c>
+      <c r="H128">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="129" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B129" s="1">
+        <v>1002601</v>
+      </c>
+      <c r="C129" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D129" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="E129">
+        <v>460</v>
+      </c>
+      <c r="F129">
+        <v>0.94</v>
+      </c>
+      <c r="G129">
+        <v>319</v>
+      </c>
+      <c r="H129">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="130" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B130" s="1">
+        <v>1002602</v>
+      </c>
+      <c r="C130" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D130" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="E130">
+        <v>1615</v>
+      </c>
+      <c r="F130">
+        <v>2</v>
+      </c>
+      <c r="G130">
+        <v>550</v>
+      </c>
+      <c r="H130">
+        <v>1300</v>
+      </c>
+    </row>
+    <row r="131" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B131" s="1">
+        <v>1002603</v>
+      </c>
+      <c r="C131" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D131" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="E131">
+        <v>800</v>
+      </c>
+      <c r="F131">
+        <v>1</v>
+      </c>
+      <c r="G131">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="132" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B132" s="1">
+        <v>1002604</v>
+      </c>
+      <c r="C132" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D132" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="E132">
+        <v>900</v>
+      </c>
+      <c r="F132">
+        <v>2</v>
+      </c>
+      <c r="G132">
+        <v>150</v>
+      </c>
+      <c r="H132">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="133" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B133" s="1">
+        <v>1002605</v>
+      </c>
+      <c r="C133" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D133" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="E133">
+        <v>900</v>
+      </c>
+      <c r="F133">
+        <v>1</v>
+      </c>
+      <c r="G133">
+        <v>450</v>
+      </c>
+      <c r="H133">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="134" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B134" s="1">
+        <v>1002701</v>
+      </c>
+      <c r="C134" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D134" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="E134">
+        <v>460</v>
+      </c>
+      <c r="F134">
+        <v>0.94</v>
+      </c>
+      <c r="G134">
+        <v>319</v>
+      </c>
+      <c r="H134">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="135" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B135" s="1">
+        <v>1002702</v>
+      </c>
+      <c r="C135" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D135" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="E135">
+        <v>1615</v>
+      </c>
+      <c r="F135">
+        <v>2</v>
+      </c>
+      <c r="G135">
+        <v>550</v>
+      </c>
+      <c r="H135">
+        <v>1300</v>
+      </c>
+    </row>
+    <row r="136" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B136" s="1">
+        <v>1002703</v>
+      </c>
+      <c r="C136" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D136" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="E136">
+        <v>800</v>
+      </c>
+      <c r="F136">
+        <v>1</v>
+      </c>
+      <c r="G136">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="137" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B137" s="1">
+        <v>1002704</v>
+      </c>
+      <c r="C137" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D137" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="E137">
+        <v>900</v>
+      </c>
+      <c r="F137">
+        <v>2</v>
+      </c>
+      <c r="G137">
+        <v>150</v>
+      </c>
+      <c r="H137">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="138" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B138" s="1">
+        <v>1002705</v>
+      </c>
+      <c r="C138" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D138" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="E138">
+        <v>900</v>
+      </c>
+      <c r="F138">
+        <v>1</v>
+      </c>
+      <c r="G138">
+        <v>450</v>
+      </c>
+      <c r="H138">
+        <v>900</v>
       </c>
     </row>
   </sheetData>

--- a/source/bin/excel/animation.xlsx
+++ b/source/bin/excel/animation.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\liqi-excel\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\quehun-cehua\liqi-excel\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{725A2B75-9961-4974-9DA0-222D8F9FC993}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{222369EE-0C03-4EE9-B47D-C77C59BF523D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="export" sheetId="2" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="329" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="389" uniqueCount="76">
   <si>
     <t>sheet</t>
   </si>
@@ -272,6 +272,28 @@
   <si>
     <t>hand_lifa</t>
     <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>hand_xiyuansiyiyu</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>hand_beiyuanlili</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>hand_dongchengxuanyin</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>hand_nanfenghua</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>hand_liyang</t>
+  </si>
+  <si>
+    <t>hand_chilin</t>
   </si>
 </sst>
 </file>
@@ -337,18 +359,7 @@
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="1">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -660,7 +671,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:O138"/>
+  <dimension ref="A1:O168"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.375" customWidth="1"/>
@@ -3864,6 +3875,678 @@
         <v>450</v>
       </c>
       <c r="H138">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="139" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B139" s="1">
+        <v>1002801</v>
+      </c>
+      <c r="C139" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D139" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="E139">
+        <v>460</v>
+      </c>
+      <c r="F139">
+        <v>0.94</v>
+      </c>
+      <c r="G139">
+        <v>319</v>
+      </c>
+      <c r="H139">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="140" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B140" s="1">
+        <v>1002802</v>
+      </c>
+      <c r="C140" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D140" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="E140">
+        <v>1615</v>
+      </c>
+      <c r="F140">
+        <v>2</v>
+      </c>
+      <c r="G140">
+        <v>550</v>
+      </c>
+      <c r="H140">
+        <v>1300</v>
+      </c>
+    </row>
+    <row r="141" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B141" s="1">
+        <v>1002803</v>
+      </c>
+      <c r="C141" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D141" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="E141">
+        <v>800</v>
+      </c>
+      <c r="F141">
+        <v>1</v>
+      </c>
+      <c r="G141">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="142" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B142" s="1">
+        <v>1002804</v>
+      </c>
+      <c r="C142" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D142" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="E142">
+        <v>900</v>
+      </c>
+      <c r="F142">
+        <v>2</v>
+      </c>
+      <c r="G142">
+        <v>150</v>
+      </c>
+      <c r="H142">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="143" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B143" s="1">
+        <v>1002805</v>
+      </c>
+      <c r="C143" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D143" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="E143">
+        <v>900</v>
+      </c>
+      <c r="F143">
+        <v>1</v>
+      </c>
+      <c r="G143">
+        <v>450</v>
+      </c>
+      <c r="H143">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="144" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B144" s="1">
+        <v>1002901</v>
+      </c>
+      <c r="C144" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D144" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="E144">
+        <v>460</v>
+      </c>
+      <c r="F144">
+        <v>0.94</v>
+      </c>
+      <c r="G144">
+        <v>319</v>
+      </c>
+      <c r="H144">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="145" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B145" s="1">
+        <v>1002902</v>
+      </c>
+      <c r="C145" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D145" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="E145">
+        <v>1615</v>
+      </c>
+      <c r="F145">
+        <v>2</v>
+      </c>
+      <c r="G145">
+        <v>550</v>
+      </c>
+      <c r="H145">
+        <v>1300</v>
+      </c>
+    </row>
+    <row r="146" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B146" s="1">
+        <v>1002903</v>
+      </c>
+      <c r="C146" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D146" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="E146">
+        <v>800</v>
+      </c>
+      <c r="F146">
+        <v>1</v>
+      </c>
+      <c r="G146">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="147" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B147" s="1">
+        <v>1002904</v>
+      </c>
+      <c r="C147" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D147" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="E147">
+        <v>900</v>
+      </c>
+      <c r="F147">
+        <v>2</v>
+      </c>
+      <c r="G147">
+        <v>150</v>
+      </c>
+      <c r="H147">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="148" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B148" s="1">
+        <v>1002905</v>
+      </c>
+      <c r="C148" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D148" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="E148">
+        <v>900</v>
+      </c>
+      <c r="F148">
+        <v>1</v>
+      </c>
+      <c r="G148">
+        <v>450</v>
+      </c>
+      <c r="H148">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="149" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B149" s="1">
+        <v>1003001</v>
+      </c>
+      <c r="C149" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D149" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="E149">
+        <v>460</v>
+      </c>
+      <c r="F149">
+        <v>0.94</v>
+      </c>
+      <c r="G149">
+        <v>319</v>
+      </c>
+      <c r="H149">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="150" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B150" s="1">
+        <v>1003002</v>
+      </c>
+      <c r="C150" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D150" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="E150">
+        <v>1615</v>
+      </c>
+      <c r="F150">
+        <v>2</v>
+      </c>
+      <c r="G150">
+        <v>550</v>
+      </c>
+      <c r="H150">
+        <v>1300</v>
+      </c>
+    </row>
+    <row r="151" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B151" s="1">
+        <v>1003003</v>
+      </c>
+      <c r="C151" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D151" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="E151">
+        <v>800</v>
+      </c>
+      <c r="F151">
+        <v>1</v>
+      </c>
+      <c r="G151">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="152" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B152" s="1">
+        <v>1003004</v>
+      </c>
+      <c r="C152" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D152" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="E152">
+        <v>900</v>
+      </c>
+      <c r="F152">
+        <v>2</v>
+      </c>
+      <c r="G152">
+        <v>150</v>
+      </c>
+      <c r="H152">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="153" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B153" s="1">
+        <v>1003005</v>
+      </c>
+      <c r="C153" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D153" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="E153">
+        <v>900</v>
+      </c>
+      <c r="F153">
+        <v>1</v>
+      </c>
+      <c r="G153">
+        <v>450</v>
+      </c>
+      <c r="H153">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="154" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B154" s="1">
+        <v>1003101</v>
+      </c>
+      <c r="C154" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D154" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="E154">
+        <v>460</v>
+      </c>
+      <c r="F154">
+        <v>0.94</v>
+      </c>
+      <c r="G154">
+        <v>319</v>
+      </c>
+      <c r="H154">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="155" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B155" s="1">
+        <v>1003102</v>
+      </c>
+      <c r="C155" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D155" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="E155">
+        <v>1615</v>
+      </c>
+      <c r="F155">
+        <v>2</v>
+      </c>
+      <c r="G155">
+        <v>550</v>
+      </c>
+      <c r="H155">
+        <v>1300</v>
+      </c>
+    </row>
+    <row r="156" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B156" s="1">
+        <v>1003103</v>
+      </c>
+      <c r="C156" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D156" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="E156">
+        <v>800</v>
+      </c>
+      <c r="F156">
+        <v>1</v>
+      </c>
+      <c r="G156">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="157" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B157" s="1">
+        <v>1003104</v>
+      </c>
+      <c r="C157" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D157" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="E157">
+        <v>900</v>
+      </c>
+      <c r="F157">
+        <v>2</v>
+      </c>
+      <c r="G157">
+        <v>150</v>
+      </c>
+      <c r="H157">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="158" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B158" s="1">
+        <v>1003105</v>
+      </c>
+      <c r="C158" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D158" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="E158">
+        <v>900</v>
+      </c>
+      <c r="F158">
+        <v>1</v>
+      </c>
+      <c r="G158">
+        <v>450</v>
+      </c>
+      <c r="H158">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="159" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B159" s="1">
+        <v>1003201</v>
+      </c>
+      <c r="C159" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D159" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E159">
+        <v>460</v>
+      </c>
+      <c r="F159">
+        <v>0.94</v>
+      </c>
+      <c r="G159">
+        <v>319</v>
+      </c>
+      <c r="H159">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="160" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B160" s="1">
+        <v>1003202</v>
+      </c>
+      <c r="C160" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D160" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E160">
+        <v>1615</v>
+      </c>
+      <c r="F160">
+        <v>2</v>
+      </c>
+      <c r="G160">
+        <v>550</v>
+      </c>
+      <c r="H160">
+        <v>1300</v>
+      </c>
+    </row>
+    <row r="161" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B161" s="1">
+        <v>1003203</v>
+      </c>
+      <c r="C161" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D161" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E161">
+        <v>800</v>
+      </c>
+      <c r="F161">
+        <v>1</v>
+      </c>
+      <c r="G161">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="162" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B162" s="1">
+        <v>1003204</v>
+      </c>
+      <c r="C162" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D162" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E162">
+        <v>900</v>
+      </c>
+      <c r="F162">
+        <v>2</v>
+      </c>
+      <c r="G162">
+        <v>150</v>
+      </c>
+      <c r="H162">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="163" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B163" s="1">
+        <v>1003205</v>
+      </c>
+      <c r="C163" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D163" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E163">
+        <v>900</v>
+      </c>
+      <c r="F163">
+        <v>1</v>
+      </c>
+      <c r="G163">
+        <v>450</v>
+      </c>
+      <c r="H163">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="164" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B164" s="1">
+        <v>1003301</v>
+      </c>
+      <c r="C164" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D164" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E164">
+        <v>460</v>
+      </c>
+      <c r="F164">
+        <v>0.94</v>
+      </c>
+      <c r="G164">
+        <v>319</v>
+      </c>
+      <c r="H164">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="165" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B165" s="1">
+        <v>1003302</v>
+      </c>
+      <c r="C165" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D165" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E165">
+        <v>1615</v>
+      </c>
+      <c r="F165">
+        <v>2</v>
+      </c>
+      <c r="G165">
+        <v>550</v>
+      </c>
+      <c r="H165">
+        <v>1300</v>
+      </c>
+    </row>
+    <row r="166" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B166" s="1">
+        <v>1003303</v>
+      </c>
+      <c r="C166" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D166" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E166">
+        <v>800</v>
+      </c>
+      <c r="F166">
+        <v>1</v>
+      </c>
+      <c r="G166">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="167" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B167" s="1">
+        <v>1003304</v>
+      </c>
+      <c r="C167" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D167" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E167">
+        <v>900</v>
+      </c>
+      <c r="F167">
+        <v>2</v>
+      </c>
+      <c r="G167">
+        <v>150</v>
+      </c>
+      <c r="H167">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="168" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B168" s="1">
+        <v>1003305</v>
+      </c>
+      <c r="C168" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D168" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E168">
+        <v>900</v>
+      </c>
+      <c r="F168">
+        <v>1</v>
+      </c>
+      <c r="G168">
+        <v>450</v>
+      </c>
+      <c r="H168">
         <v>900</v>
       </c>
     </row>
